--- a/output/centralitetsmål.xlsx
+++ b/output/centralitetsmål.xlsx
@@ -444,7 +444,7 @@
         <v>9</v>
       </c>
       <c r="E2">
-        <v>0.02422987652976198</v>
+        <v>0.02422987652976197</v>
       </c>
       <c r="F2">
         <v>0.000946073793755913</v>
@@ -465,7 +465,7 @@
         <v>58</v>
       </c>
       <c r="L2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M2">
         <v>195</v>
@@ -492,7 +492,7 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0.3597247389187725</v>
+        <v>0.3597247389187728</v>
       </c>
       <c r="F3">
         <v>0.00109051254089422</v>
@@ -540,7 +540,7 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>0.09477273339112659</v>
+        <v>0.09477273339112645</v>
       </c>
       <c r="F4">
         <v>0.0011001100110011</v>
@@ -561,7 +561,7 @@
         <v>43</v>
       </c>
       <c r="L4">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M4">
         <v>96</v>
@@ -588,7 +588,7 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>0.02946908586509006</v>
+        <v>0.02946908586509003</v>
       </c>
       <c r="F5">
         <v>0.000999000999000999</v>
@@ -609,7 +609,7 @@
         <v>55</v>
       </c>
       <c r="L5">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M5">
         <v>163</v>
@@ -636,7 +636,7 @@
         <v>9</v>
       </c>
       <c r="E6">
-        <v>0.03822553571129243</v>
+        <v>0.0382255357112924</v>
       </c>
       <c r="F6">
         <v>0.00101419878296146</v>
@@ -657,7 +657,7 @@
         <v>58</v>
       </c>
       <c r="L6">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="M6">
         <v>153</v>
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>0.02619460588570612</v>
+        <v>0.0261946058857061</v>
       </c>
       <c r="F7">
         <v>0.0009624639076034649</v>
@@ -705,7 +705,7 @@
         <v>56</v>
       </c>
       <c r="L7">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="M7">
         <v>185</v>
@@ -732,7 +732,7 @@
         <v>16</v>
       </c>
       <c r="E8">
-        <v>0.0434411957615994</v>
+        <v>0.04344119576159935</v>
       </c>
       <c r="F8">
         <v>0.00102880658436214</v>
@@ -753,7 +753,7 @@
         <v>51</v>
       </c>
       <c r="L8">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M8">
         <v>142</v>
@@ -801,7 +801,7 @@
         <v>65</v>
       </c>
       <c r="L9">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="M9">
         <v>234</v>
@@ -828,7 +828,7 @@
         <v>2</v>
       </c>
       <c r="E10">
-        <v>0.01031346642453009</v>
+        <v>0.0103134664245301</v>
       </c>
       <c r="F10">
         <v>0.0008319467554076539</v>
@@ -849,7 +849,7 @@
         <v>65</v>
       </c>
       <c r="L10">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="M10">
         <v>236</v>
@@ -876,7 +876,7 @@
         <v>4</v>
       </c>
       <c r="E11">
-        <v>0.0163149390982794</v>
+        <v>0.01631493909827942</v>
       </c>
       <c r="F11">
         <v>0.0008583690987124463</v>
@@ -897,7 +897,7 @@
         <v>63</v>
       </c>
       <c r="L11">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="M11">
         <v>230</v>
@@ -924,7 +924,7 @@
         <v>11</v>
       </c>
       <c r="E12">
-        <v>0.049975795586663</v>
+        <v>0.04997579558666295</v>
       </c>
       <c r="F12">
         <v>0.001018329938900204</v>
@@ -993,7 +993,7 @@
         <v>56</v>
       </c>
       <c r="L13">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M13">
         <v>117</v>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="E14">
-        <v>0.0707800696486546</v>
+        <v>0.07078006964865448</v>
       </c>
       <c r="F14">
         <v>0.001128668171557562</v>
@@ -1041,7 +1041,7 @@
         <v>51</v>
       </c>
       <c r="L14">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M14">
         <v>80</v>
@@ -1068,7 +1068,7 @@
         <v>13</v>
       </c>
       <c r="E15">
-        <v>0.06767845978722908</v>
+        <v>0.06767845978722907</v>
       </c>
       <c r="F15">
         <v>0.001109877913429523</v>
@@ -1089,7 +1089,7 @@
         <v>54</v>
       </c>
       <c r="L15">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M15">
         <v>90</v>
@@ -1116,7 +1116,7 @@
         <v>44</v>
       </c>
       <c r="E16">
-        <v>0.7043215922530729</v>
+        <v>0.7043215922530736</v>
       </c>
       <c r="F16">
         <v>0.001152073732718894</v>
@@ -1164,7 +1164,7 @@
         <v>18</v>
       </c>
       <c r="E17">
-        <v>0.1068564620204909</v>
+        <v>0.1068564620204908</v>
       </c>
       <c r="F17">
         <v>0.001104972375690608</v>
@@ -1212,7 +1212,7 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>0.05833695255091867</v>
+        <v>0.05833695255091872</v>
       </c>
       <c r="F18">
         <v>0.0009416195856873823</v>
@@ -1260,7 +1260,7 @@
         <v>21</v>
       </c>
       <c r="E19">
-        <v>0.1070975403247837</v>
+        <v>0.1070975403247836</v>
       </c>
       <c r="F19">
         <v>0.001101321585903084</v>
@@ -1308,7 +1308,7 @@
         <v>18</v>
       </c>
       <c r="E20">
-        <v>0.09080254662677734</v>
+        <v>0.09080254662677728</v>
       </c>
       <c r="F20">
         <v>0.001104972375690608</v>
@@ -1329,7 +1329,7 @@
         <v>49</v>
       </c>
       <c r="L20">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="M20">
         <v>93</v>
@@ -1404,7 +1404,7 @@
         <v>73</v>
       </c>
       <c r="E22">
-        <v>0.8159579739205558</v>
+        <v>0.8159579739205566</v>
       </c>
       <c r="F22">
         <v>0.001243781094527363</v>
@@ -1452,7 +1452,7 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>0.0217892126691482</v>
+        <v>0.02178921266914818</v>
       </c>
       <c r="F23">
         <v>0.000946073793755913</v>
@@ -1473,7 +1473,7 @@
         <v>60</v>
       </c>
       <c r="L23">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M23">
         <v>195</v>
@@ -1500,7 +1500,7 @@
         <v>12</v>
       </c>
       <c r="E24">
-        <v>0.07482741768511489</v>
+        <v>0.07482741768511485</v>
       </c>
       <c r="F24">
         <v>0.001053740779768177</v>
@@ -1521,7 +1521,7 @@
         <v>55</v>
       </c>
       <c r="L24">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M24">
         <v>124</v>
@@ -1548,7 +1548,7 @@
         <v>18</v>
       </c>
       <c r="E25">
-        <v>0.09665848679786822</v>
+        <v>0.09665848679786826</v>
       </c>
       <c r="F25">
         <v>0.001126126126126126</v>
@@ -1569,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="L25">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M25">
         <v>82</v>
@@ -1596,7 +1596,7 @@
         <v>15</v>
       </c>
       <c r="E26">
-        <v>0.04655049166843661</v>
+        <v>0.04655049166843651</v>
       </c>
       <c r="F26">
         <v>0.001064962726304579</v>
@@ -1617,7 +1617,7 @@
         <v>52</v>
       </c>
       <c r="L26">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M26">
         <v>117</v>
@@ -1644,7 +1644,7 @@
         <v>7</v>
       </c>
       <c r="E27">
-        <v>0.02066318361114046</v>
+        <v>0.02066318361114044</v>
       </c>
       <c r="F27">
         <v>0.0009689922480620155</v>
@@ -1665,7 +1665,7 @@
         <v>60</v>
       </c>
       <c r="L27">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M27">
         <v>181</v>
@@ -1692,7 +1692,7 @@
         <v>60</v>
       </c>
       <c r="E28">
-        <v>0.791785181105089</v>
+        <v>0.7917851811050894</v>
       </c>
       <c r="F28">
         <v>0.001191895113230036</v>
@@ -1740,7 +1740,7 @@
         <v>34</v>
       </c>
       <c r="E29">
-        <v>0.6055366250143841</v>
+        <v>0.6055366250143845</v>
       </c>
       <c r="F29">
         <v>0.001131221719457014</v>
@@ -1788,7 +1788,7 @@
         <v>9</v>
       </c>
       <c r="E30">
-        <v>0.07054021369089328</v>
+        <v>0.07054021369089332</v>
       </c>
       <c r="F30">
         <v>0.0009727626459143969</v>
@@ -1809,7 +1809,7 @@
         <v>58</v>
       </c>
       <c r="L30">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="M30">
         <v>179</v>
@@ -1836,7 +1836,7 @@
         <v>48</v>
       </c>
       <c r="E31">
-        <v>0.6086233566200452</v>
+        <v>0.6086233566200454</v>
       </c>
       <c r="F31">
         <v>0.001303780964797914</v>
@@ -1884,7 +1884,7 @@
         <v>83</v>
       </c>
       <c r="E32">
-        <v>0.9862260697372836</v>
+        <v>0.986226069737284</v>
       </c>
       <c r="F32">
         <v>0.001392757660167131</v>
@@ -1932,7 +1932,7 @@
         <v>48</v>
       </c>
       <c r="E33">
-        <v>0.7056487517509963</v>
+        <v>0.7056487517509969</v>
       </c>
       <c r="F33">
         <v>0.001197604790419162</v>
@@ -1980,7 +1980,7 @@
         <v>28</v>
       </c>
       <c r="E34">
-        <v>0.2631824894973781</v>
+        <v>0.2631824894973778</v>
       </c>
       <c r="F34">
         <v>0.00120918984280532</v>
@@ -2028,7 +2028,7 @@
         <v>4</v>
       </c>
       <c r="E35">
-        <v>0.007830241130870028</v>
+        <v>0.00783024113087003</v>
       </c>
       <c r="F35">
         <v>0.0008658008658008658</v>
@@ -2049,7 +2049,7 @@
         <v>63</v>
       </c>
       <c r="L35">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="M35">
         <v>229</v>
@@ -2097,7 +2097,7 @@
         <v>57</v>
       </c>
       <c r="L36">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M36">
         <v>180</v>
@@ -2124,7 +2124,7 @@
         <v>25</v>
       </c>
       <c r="E37">
-        <v>0.1125376529405955</v>
+        <v>0.1125376529405953</v>
       </c>
       <c r="F37">
         <v>0.001118568232662192</v>
@@ -2172,7 +2172,7 @@
         <v>18</v>
       </c>
       <c r="E38">
-        <v>0.06744819057089387</v>
+        <v>0.0674481905708937</v>
       </c>
       <c r="F38">
         <v>0.001042752867570386</v>
@@ -2193,7 +2193,7 @@
         <v>49</v>
       </c>
       <c r="L38">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M38">
         <v>132</v>
@@ -2220,7 +2220,7 @@
         <v>24</v>
       </c>
       <c r="E39">
-        <v>0.104250380012344</v>
+        <v>0.1042503800123439</v>
       </c>
       <c r="F39">
         <v>0.00112739571589628</v>
@@ -2316,7 +2316,7 @@
         <v>20</v>
       </c>
       <c r="E41">
-        <v>0.04472965983498278</v>
+        <v>0.04472965983498276</v>
       </c>
       <c r="F41">
         <v>0.001030927835051546</v>
@@ -2337,7 +2337,7 @@
         <v>47</v>
       </c>
       <c r="L41">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M41">
         <v>140</v>
@@ -2364,7 +2364,7 @@
         <v>9</v>
       </c>
       <c r="E42">
-        <v>0.03309968498653235</v>
+        <v>0.03309968498653239</v>
       </c>
       <c r="F42">
         <v>0.0009633911368015414</v>
@@ -2385,7 +2385,7 @@
         <v>58</v>
       </c>
       <c r="L42">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M42">
         <v>184</v>
@@ -2412,7 +2412,7 @@
         <v>47</v>
       </c>
       <c r="E43">
-        <v>0.2905787932077578</v>
+        <v>0.2905787932077576</v>
       </c>
       <c r="F43">
         <v>0.001243781094527363</v>
@@ -2460,7 +2460,7 @@
         <v>18</v>
       </c>
       <c r="E44">
-        <v>0.0654907932755863</v>
+        <v>0.0654907932755862</v>
       </c>
       <c r="F44">
         <v>0.00109051254089422</v>
@@ -2481,7 +2481,7 @@
         <v>49</v>
       </c>
       <c r="L44">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M44">
         <v>102</v>
@@ -2508,7 +2508,7 @@
         <v>20</v>
       </c>
       <c r="E45">
-        <v>0.08361033988870654</v>
+        <v>0.08361033988870653</v>
       </c>
       <c r="F45">
         <v>0.001017293997965412</v>
@@ -2529,7 +2529,7 @@
         <v>47</v>
       </c>
       <c r="L45">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M45">
         <v>150</v>
@@ -2556,7 +2556,7 @@
         <v>29</v>
       </c>
       <c r="E46">
-        <v>0.1409971730038432</v>
+        <v>0.140997173003843</v>
       </c>
       <c r="F46">
         <v>0.001183431952662722</v>
@@ -2604,7 +2604,7 @@
         <v>10</v>
       </c>
       <c r="E47">
-        <v>0.03515262443037627</v>
+        <v>0.03515262443037621</v>
       </c>
       <c r="F47">
         <v>0.0009900990099009901</v>
@@ -2625,7 +2625,7 @@
         <v>57</v>
       </c>
       <c r="L47">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M47">
         <v>170</v>
@@ -2652,7 +2652,7 @@
         <v>16</v>
       </c>
       <c r="E48">
-        <v>0.0267163185563241</v>
+        <v>0.02671631855632408</v>
       </c>
       <c r="F48">
         <v>0.0009310986964618249</v>
@@ -2673,7 +2673,7 @@
         <v>51</v>
       </c>
       <c r="L48">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="M48">
         <v>203</v>
@@ -2700,7 +2700,7 @@
         <v>18</v>
       </c>
       <c r="E49">
-        <v>0.2761148991297415</v>
+        <v>0.276114899129742</v>
       </c>
       <c r="F49">
         <v>0.001003009027081244</v>
@@ -2748,7 +2748,7 @@
         <v>5</v>
       </c>
       <c r="E50">
-        <v>0.01248617680035849</v>
+        <v>0.01248617680035847</v>
       </c>
       <c r="F50">
         <v>0.0009310986964618249</v>
@@ -2769,7 +2769,7 @@
         <v>62</v>
       </c>
       <c r="L50">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="M50">
         <v>203</v>
@@ -2844,7 +2844,7 @@
         <v>13</v>
       </c>
       <c r="E52">
-        <v>0.04421824735934708</v>
+        <v>0.0442182473593471</v>
       </c>
       <c r="F52">
         <v>0.001021450459652707</v>
@@ -2865,7 +2865,7 @@
         <v>54</v>
       </c>
       <c r="L52">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="M52">
         <v>147</v>
@@ -2940,7 +2940,7 @@
         <v>9</v>
       </c>
       <c r="E54">
-        <v>0.07186647685747065</v>
+        <v>0.07186647685747062</v>
       </c>
       <c r="F54">
         <v>0.001058201058201058</v>
@@ -2961,7 +2961,7 @@
         <v>58</v>
       </c>
       <c r="L54">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M54">
         <v>122</v>
@@ -2988,7 +2988,7 @@
         <v>35</v>
       </c>
       <c r="E55">
-        <v>0.6192606169279937</v>
+        <v>0.6192606169279944</v>
       </c>
       <c r="F55">
         <v>0.001146788990825688</v>
@@ -3036,7 +3036,7 @@
         <v>25</v>
       </c>
       <c r="E56">
-        <v>0.09140976170902959</v>
+        <v>0.09140976170902942</v>
       </c>
       <c r="F56">
         <v>0.001128668171557562</v>
@@ -3057,7 +3057,7 @@
         <v>42</v>
       </c>
       <c r="L56">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="M56">
         <v>80</v>
@@ -3084,7 +3084,7 @@
         <v>20</v>
       </c>
       <c r="E57">
-        <v>0.08554141832195952</v>
+        <v>0.08554141832195944</v>
       </c>
       <c r="F57">
         <v>0.001121076233183856</v>
@@ -3105,7 +3105,7 @@
         <v>47</v>
       </c>
       <c r="L57">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M57">
         <v>85</v>
@@ -3132,7 +3132,7 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>0.004466201652518955</v>
+        <v>0.004466201652518942</v>
       </c>
       <c r="F58">
         <v>0.0007905138339920949</v>
@@ -3153,7 +3153,7 @@
         <v>65</v>
       </c>
       <c r="L58">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M58">
         <v>243</v>
@@ -3180,7 +3180,7 @@
         <v>10</v>
       </c>
       <c r="E59">
-        <v>0.03098946147202335</v>
+        <v>0.03098946147202334</v>
       </c>
       <c r="F59">
         <v>0.0009775171065493646</v>
@@ -3201,7 +3201,7 @@
         <v>57</v>
       </c>
       <c r="L59">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M59">
         <v>176</v>
@@ -3228,7 +3228,7 @@
         <v>21</v>
       </c>
       <c r="E60">
-        <v>0.09416823195343527</v>
+        <v>0.09416823195343518</v>
       </c>
       <c r="F60">
         <v>0.001085776330076004</v>
@@ -3249,7 +3249,7 @@
         <v>46</v>
       </c>
       <c r="L60">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M60">
         <v>106</v>
@@ -3324,7 +3324,7 @@
         <v>49</v>
       </c>
       <c r="E62">
-        <v>0.1892244562698276</v>
+        <v>0.1892244562698275</v>
       </c>
       <c r="F62">
         <v>0.001207729468599034</v>
@@ -3393,7 +3393,7 @@
         <v>63</v>
       </c>
       <c r="L63">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M63">
         <v>204</v>
@@ -3420,7 +3420,7 @@
         <v>31</v>
       </c>
       <c r="E64">
-        <v>0.326689660113803</v>
+        <v>0.3266896601138031</v>
       </c>
       <c r="F64">
         <v>0.001074113856068743</v>
@@ -3468,7 +3468,7 @@
         <v>52</v>
       </c>
       <c r="E65">
-        <v>0.8116952369455204</v>
+        <v>0.8116952369455207</v>
       </c>
       <c r="F65">
         <v>0.001303780964797914</v>
@@ -3537,7 +3537,7 @@
         <v>61</v>
       </c>
       <c r="L66">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="M66">
         <v>223</v>
@@ -3564,7 +3564,7 @@
         <v>10</v>
       </c>
       <c r="E67">
-        <v>0.0407669023522735</v>
+        <v>0.04076690235227347</v>
       </c>
       <c r="F67">
         <v>0.00103950103950104</v>
@@ -3585,7 +3585,7 @@
         <v>57</v>
       </c>
       <c r="L67">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M67">
         <v>134</v>
@@ -3681,7 +3681,7 @@
         <v>61</v>
       </c>
       <c r="L69">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M69">
         <v>126</v>
@@ -3708,7 +3708,7 @@
         <v>44</v>
       </c>
       <c r="E70">
-        <v>0.6833333812144426</v>
+        <v>0.6833333812144431</v>
       </c>
       <c r="F70">
         <v>0.001172332942555686</v>
@@ -3756,7 +3756,7 @@
         <v>9</v>
       </c>
       <c r="E71">
-        <v>0.04239304462352322</v>
+        <v>0.04239304462352323</v>
       </c>
       <c r="F71">
         <v>0.0009970089730807576</v>
@@ -3777,7 +3777,7 @@
         <v>58</v>
       </c>
       <c r="L71">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M71">
         <v>165</v>
@@ -3804,7 +3804,7 @@
         <v>22</v>
       </c>
       <c r="E72">
-        <v>0.1031341240443447</v>
+        <v>0.1031341240443445</v>
       </c>
       <c r="F72">
         <v>0.001118568232662192</v>
@@ -3852,7 +3852,7 @@
         <v>13</v>
       </c>
       <c r="E73">
-        <v>0.09226709445031589</v>
+        <v>0.09226709445031578</v>
       </c>
       <c r="F73">
         <v>0.001060445387062566</v>
@@ -3873,7 +3873,7 @@
         <v>54</v>
       </c>
       <c r="L73">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M73">
         <v>120</v>
@@ -3900,7 +3900,7 @@
         <v>13</v>
       </c>
       <c r="E74">
-        <v>0.06132849901000579</v>
+        <v>0.06132849901000576</v>
       </c>
       <c r="F74">
         <v>0.001048218029350105</v>
@@ -3921,7 +3921,7 @@
         <v>54</v>
       </c>
       <c r="L74">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="M74">
         <v>129</v>
@@ -3948,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="E75">
-        <v>0.06132849901000579</v>
+        <v>0.06132849901000578</v>
       </c>
       <c r="F75">
         <v>0.001048218029350105</v>
@@ -3969,7 +3969,7 @@
         <v>54</v>
       </c>
       <c r="L75">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M75">
         <v>129</v>
@@ -3996,7 +3996,7 @@
         <v>13</v>
       </c>
       <c r="E76">
-        <v>0.06132849901000579</v>
+        <v>0.06132849901000575</v>
       </c>
       <c r="F76">
         <v>0.001048218029350105</v>
@@ -4044,7 +4044,7 @@
         <v>11</v>
       </c>
       <c r="E77">
-        <v>0.04477113103965424</v>
+        <v>0.0447711310396542</v>
       </c>
       <c r="F77">
         <v>0.001021450459652707</v>
@@ -4065,7 +4065,7 @@
         <v>56</v>
       </c>
       <c r="L77">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M77">
         <v>147</v>
@@ -4092,7 +4092,7 @@
         <v>13</v>
       </c>
       <c r="E78">
-        <v>0.06009935512153929</v>
+        <v>0.06009935512153926</v>
       </c>
       <c r="F78">
         <v>0.001097694840834248</v>
@@ -4140,7 +4140,7 @@
         <v>19</v>
       </c>
       <c r="E79">
-        <v>0.1392291044062632</v>
+        <v>0.139229104406263</v>
       </c>
       <c r="F79">
         <v>0.001135073779795687</v>
@@ -4188,7 +4188,7 @@
         <v>32</v>
       </c>
       <c r="E80">
-        <v>0.1837423579642064</v>
+        <v>0.1837423579642063</v>
       </c>
       <c r="F80">
         <v>0.001184834123222749</v>
@@ -4236,7 +4236,7 @@
         <v>39</v>
       </c>
       <c r="E81">
-        <v>0.6486459323812122</v>
+        <v>0.6486459323812123</v>
       </c>
       <c r="F81">
         <v>0.001199040767386091</v>
@@ -4284,7 +4284,7 @@
         <v>6</v>
       </c>
       <c r="E82">
-        <v>0.01005286499759184</v>
+        <v>0.01005286499759183</v>
       </c>
       <c r="F82">
         <v>0.0008695652173913044</v>
@@ -4305,7 +4305,7 @@
         <v>61</v>
       </c>
       <c r="L82">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="M82">
         <v>226</v>
@@ -4332,7 +4332,7 @@
         <v>56</v>
       </c>
       <c r="E83">
-        <v>0.7438588849400156</v>
+        <v>0.7438588849400157</v>
       </c>
       <c r="F83">
         <v>0.001282051282051282</v>
@@ -4380,7 +4380,7 @@
         <v>22</v>
       </c>
       <c r="E84">
-        <v>0.08069788103815614</v>
+        <v>0.08069788103815603</v>
       </c>
       <c r="F84">
         <v>0.001071811361200429</v>
@@ -4401,7 +4401,7 @@
         <v>45</v>
       </c>
       <c r="L84">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M84">
         <v>114</v>
@@ -4428,7 +4428,7 @@
         <v>18</v>
       </c>
       <c r="E85">
-        <v>0.07073477316263428</v>
+        <v>0.07073477316263418</v>
       </c>
       <c r="F85">
         <v>0.001050420168067227</v>
@@ -4449,7 +4449,7 @@
         <v>49</v>
       </c>
       <c r="L85">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M85">
         <v>127</v>
@@ -4476,7 +4476,7 @@
         <v>22</v>
       </c>
       <c r="E86">
-        <v>0.1912420051322477</v>
+        <v>0.1912420051322479</v>
       </c>
       <c r="F86">
         <v>0.001118568232662192</v>
@@ -4524,7 +4524,7 @@
         <v>77</v>
       </c>
       <c r="E87">
-        <v>0.9156380386813004</v>
+        <v>0.915638038681301</v>
       </c>
       <c r="F87">
         <v>0.001385041551246537</v>
@@ -4593,7 +4593,7 @@
         <v>56</v>
       </c>
       <c r="L88">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M88">
         <v>178</v>
@@ -4620,7 +4620,7 @@
         <v>44</v>
       </c>
       <c r="E89">
-        <v>0.4528611252341563</v>
+        <v>0.4528611252341562</v>
       </c>
       <c r="F89">
         <v>0.0012531328320802</v>
@@ -4668,7 +4668,7 @@
         <v>46</v>
       </c>
       <c r="E90">
-        <v>0.4156427643534553</v>
+        <v>0.4156427643534551</v>
       </c>
       <c r="F90">
         <v>0.00130890052356021</v>
@@ -4716,7 +4716,7 @@
         <v>11</v>
       </c>
       <c r="E91">
-        <v>0.03514642359250851</v>
+        <v>0.03514642359250852</v>
       </c>
       <c r="F91">
         <v>0.001</v>
@@ -4737,7 +4737,7 @@
         <v>56</v>
       </c>
       <c r="L91">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M91">
         <v>162</v>
@@ -4764,7 +4764,7 @@
         <v>12</v>
       </c>
       <c r="E92">
-        <v>0.1595480143597212</v>
+        <v>0.1595480143597214</v>
       </c>
       <c r="F92">
         <v>0.0009930486593843098</v>
@@ -4812,7 +4812,7 @@
         <v>38</v>
       </c>
       <c r="E93">
-        <v>0.2112571891289693</v>
+        <v>0.2112571891289692</v>
       </c>
       <c r="F93">
         <v>0.001234567901234568</v>
@@ -4860,7 +4860,7 @@
         <v>3</v>
       </c>
       <c r="E94">
-        <v>0.01778052030393817</v>
+        <v>0.01778052030393819</v>
       </c>
       <c r="F94">
         <v>0.0008525149190110827</v>
@@ -4881,7 +4881,7 @@
         <v>64</v>
       </c>
       <c r="L94">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="M94">
         <v>231</v>
@@ -4908,7 +4908,7 @@
         <v>37</v>
       </c>
       <c r="E95">
-        <v>0.6303335694729009</v>
+        <v>0.6303335694729013</v>
       </c>
       <c r="F95">
         <v>0.001138952164009112</v>
@@ -4956,7 +4956,7 @@
         <v>10</v>
       </c>
       <c r="E96">
-        <v>0.05316632598305136</v>
+        <v>0.05316632598305138</v>
       </c>
       <c r="F96">
         <v>0.0009433962264150943</v>
@@ -5004,7 +5004,7 @@
         <v>32</v>
       </c>
       <c r="E97">
-        <v>0.1239882248057652</v>
+        <v>0.1239882248057651</v>
       </c>
       <c r="F97">
         <v>0.001230012300123001</v>
@@ -5052,7 +5052,7 @@
         <v>28</v>
       </c>
       <c r="E98">
-        <v>0.3771274965687756</v>
+        <v>0.377127496568776</v>
       </c>
       <c r="F98">
         <v>0.00115606936416185</v>
@@ -5148,7 +5148,7 @@
         <v>13</v>
       </c>
       <c r="E100">
-        <v>0.03792059464596581</v>
+        <v>0.03792059464596578</v>
       </c>
       <c r="F100">
         <v>0.001051524710830704</v>
@@ -5169,7 +5169,7 @@
         <v>54</v>
       </c>
       <c r="L100">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="M100">
         <v>126</v>
@@ -5196,7 +5196,7 @@
         <v>12</v>
       </c>
       <c r="E101">
-        <v>0.09667574350587989</v>
+        <v>0.0966757435058799</v>
       </c>
       <c r="F101">
         <v>0.001089324618736384</v>
@@ -5217,7 +5217,7 @@
         <v>55</v>
       </c>
       <c r="L101">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="M101">
         <v>103</v>
@@ -5265,7 +5265,7 @@
         <v>64</v>
       </c>
       <c r="L102">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="M102">
         <v>222</v>
@@ -5292,7 +5292,7 @@
         <v>44</v>
       </c>
       <c r="E103">
-        <v>0.6856372330789423</v>
+        <v>0.6856372330789425</v>
       </c>
       <c r="F103">
         <v>0.001237623762376238</v>
@@ -5340,7 +5340,7 @@
         <v>25</v>
       </c>
       <c r="E104">
-        <v>0.1002670983026586</v>
+        <v>0.1002670983026585</v>
       </c>
       <c r="F104">
         <v>0.001123595505617978</v>
@@ -5388,7 +5388,7 @@
         <v>14</v>
       </c>
       <c r="E105">
-        <v>0.07932897301161758</v>
+        <v>0.07932897301161752</v>
       </c>
       <c r="F105">
         <v>0.001122334455667789</v>
@@ -5409,7 +5409,7 @@
         <v>53</v>
       </c>
       <c r="L105">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M105">
         <v>84</v>
@@ -5484,7 +5484,7 @@
         <v>13</v>
       </c>
       <c r="E107">
-        <v>0.03070752643984765</v>
+        <v>0.03070752643984763</v>
       </c>
       <c r="F107">
         <v>0.0009940357852882703</v>
@@ -5505,7 +5505,7 @@
         <v>54</v>
       </c>
       <c r="L107">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="M107">
         <v>167</v>
@@ -5532,7 +5532,7 @@
         <v>46</v>
       </c>
       <c r="E108">
-        <v>0.6547962135334694</v>
+        <v>0.6547962135334698</v>
       </c>
       <c r="F108">
         <v>0.001199040767386091</v>
@@ -5628,7 +5628,7 @@
         <v>20</v>
       </c>
       <c r="E110">
-        <v>0.292280656256971</v>
+        <v>0.2922806562569711</v>
       </c>
       <c r="F110">
         <v>0.0011001100110011</v>
@@ -5676,7 +5676,7 @@
         <v>49</v>
       </c>
       <c r="E111">
-        <v>0.7362696350395049</v>
+        <v>0.7362696350395052</v>
       </c>
       <c r="F111">
         <v>0.001226993865030675</v>
@@ -5724,7 +5724,7 @@
         <v>9</v>
       </c>
       <c r="E112">
-        <v>0.04511268027960581</v>
+        <v>0.04511268027960575</v>
       </c>
       <c r="F112">
         <v>0.001016260162601626</v>
@@ -5745,7 +5745,7 @@
         <v>58</v>
       </c>
       <c r="L112">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M112">
         <v>151</v>
@@ -5772,7 +5772,7 @@
         <v>14</v>
       </c>
       <c r="E113">
-        <v>0.1465501445762345</v>
+        <v>0.1465501445762347</v>
       </c>
       <c r="F113">
         <v>0.0009930486593843098</v>
@@ -5820,7 +5820,7 @@
         <v>12</v>
       </c>
       <c r="E114">
-        <v>0.03962566269671144</v>
+        <v>0.03962566269671137</v>
       </c>
       <c r="F114">
         <v>0.001031991744066047</v>
@@ -5841,7 +5841,7 @@
         <v>55</v>
       </c>
       <c r="L114">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M114">
         <v>139</v>
@@ -5868,7 +5868,7 @@
         <v>54</v>
       </c>
       <c r="E115">
-        <v>0.4838893095742893</v>
+        <v>0.4838893095742895</v>
       </c>
       <c r="F115">
         <v>0.001297016861219196</v>
@@ -5916,7 +5916,7 @@
         <v>85</v>
       </c>
       <c r="E116">
-        <v>0.5952655989474596</v>
+        <v>0.5952655989474599</v>
       </c>
       <c r="F116">
         <v>0.001388888888888889</v>
@@ -6012,7 +6012,7 @@
         <v>17</v>
       </c>
       <c r="E118">
-        <v>0.1716162433726338</v>
+        <v>0.1716162433726337</v>
       </c>
       <c r="F118">
         <v>0.001118568232662192</v>
@@ -6060,7 +6060,7 @@
         <v>16</v>
       </c>
       <c r="E119">
-        <v>0.0942138685114981</v>
+        <v>0.09421386851149806</v>
       </c>
       <c r="F119">
         <v>0.001111111111111111</v>
@@ -6081,7 +6081,7 @@
         <v>51</v>
       </c>
       <c r="L119">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M119">
         <v>89</v>
@@ -6108,7 +6108,7 @@
         <v>23</v>
       </c>
       <c r="E120">
-        <v>0.1998729100110433</v>
+        <v>0.1998729100110432</v>
       </c>
       <c r="F120">
         <v>0.001136363636363636</v>
@@ -6177,7 +6177,7 @@
         <v>48</v>
       </c>
       <c r="L121">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M121">
         <v>107</v>
@@ -6204,7 +6204,7 @@
         <v>78</v>
       </c>
       <c r="E122">
-        <v>0.5987390984672721</v>
+        <v>0.5987390984672724</v>
       </c>
       <c r="F122">
         <v>0.001362397820163488</v>
@@ -6252,7 +6252,7 @@
         <v>13</v>
       </c>
       <c r="E123">
-        <v>0.08146914630702831</v>
+        <v>0.08146914630702838</v>
       </c>
       <c r="F123">
         <v>0.001034126163391934</v>
@@ -6273,7 +6273,7 @@
         <v>54</v>
       </c>
       <c r="L123">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M123">
         <v>137</v>
@@ -6300,7 +6300,7 @@
         <v>81</v>
       </c>
       <c r="E124">
-        <v>0.9528996523255167</v>
+        <v>0.952899652325517</v>
       </c>
       <c r="F124">
         <v>0.001408450704225352</v>
@@ -6348,7 +6348,7 @@
         <v>55</v>
       </c>
       <c r="E125">
-        <v>0.8029541936357731</v>
+        <v>0.8029541936357739</v>
       </c>
       <c r="F125">
         <v>0.001295336787564767</v>
@@ -6396,7 +6396,7 @@
         <v>4</v>
       </c>
       <c r="E126">
-        <v>0.005592742149896759</v>
+        <v>0.005592742149896761</v>
       </c>
       <c r="F126">
         <v>0.0008410428931875525</v>
@@ -6417,7 +6417,7 @@
         <v>63</v>
       </c>
       <c r="L126">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="M126">
         <v>235</v>
@@ -6444,7 +6444,7 @@
         <v>11</v>
       </c>
       <c r="E127">
-        <v>0.03509298668937987</v>
+        <v>0.03509298668937989</v>
       </c>
       <c r="F127">
         <v>0.0009587727708533077</v>
@@ -6465,7 +6465,7 @@
         <v>56</v>
       </c>
       <c r="L127">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M127">
         <v>187</v>
@@ -6492,7 +6492,7 @@
         <v>16</v>
       </c>
       <c r="E128">
-        <v>0.07172077918312188</v>
+        <v>0.07172077918312186</v>
       </c>
       <c r="F128">
         <v>0.001104972375690608</v>
@@ -6513,7 +6513,7 @@
         <v>51</v>
       </c>
       <c r="L128">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M128">
         <v>93</v>
@@ -6540,7 +6540,7 @@
         <v>12</v>
       </c>
       <c r="E129">
-        <v>0.06304443887997588</v>
+        <v>0.06304443887997585</v>
       </c>
       <c r="F129">
         <v>0.001036269430051813</v>
@@ -6561,7 +6561,7 @@
         <v>55</v>
       </c>
       <c r="L129">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="M129">
         <v>136</v>
@@ -6588,7 +6588,7 @@
         <v>43</v>
       </c>
       <c r="E130">
-        <v>0.3105602898847384</v>
+        <v>0.3105602898847386</v>
       </c>
       <c r="F130">
         <v>0.001291989664082687</v>
@@ -6684,7 +6684,7 @@
         <v>13</v>
       </c>
       <c r="E132">
-        <v>0.09164842022329846</v>
+        <v>0.09164842022329839</v>
       </c>
       <c r="F132">
         <v>0.001059322033898305</v>
@@ -6705,7 +6705,7 @@
         <v>54</v>
       </c>
       <c r="L132">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M132">
         <v>121</v>
@@ -6732,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="E133">
-        <v>0.1000616040012356</v>
+        <v>0.1000616040012357</v>
       </c>
       <c r="F133">
         <v>0.001084598698481562</v>
@@ -6753,7 +6753,7 @@
         <v>52</v>
       </c>
       <c r="L133">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M133">
         <v>107</v>
@@ -6780,7 +6780,7 @@
         <v>14</v>
       </c>
       <c r="E134">
-        <v>0.1027971265220745</v>
+        <v>0.1027971265220744</v>
       </c>
       <c r="F134">
         <v>0.001066098081023454</v>
@@ -6828,7 +6828,7 @@
         <v>15</v>
       </c>
       <c r="E135">
-        <v>0.1000616040012356</v>
+        <v>0.1000616040012357</v>
       </c>
       <c r="F135">
         <v>0.001084598698481562</v>
@@ -6876,7 +6876,7 @@
         <v>16</v>
       </c>
       <c r="E136">
-        <v>0.06545820001331439</v>
+        <v>0.06545820001331437</v>
       </c>
       <c r="F136">
         <v>0.001072961373390558</v>
@@ -6897,7 +6897,7 @@
         <v>51</v>
       </c>
       <c r="L136">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M136">
         <v>113</v>
@@ -6945,7 +6945,7 @@
         <v>61</v>
       </c>
       <c r="L137">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="M137">
         <v>205</v>
@@ -6972,7 +6972,7 @@
         <v>10</v>
       </c>
       <c r="E138">
-        <v>0.04406312821663298</v>
+        <v>0.04406312821663293</v>
       </c>
       <c r="F138">
         <v>0.001030927835051546</v>
@@ -6993,7 +6993,7 @@
         <v>57</v>
       </c>
       <c r="L138">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M138">
         <v>140</v>
@@ -7020,7 +7020,7 @@
         <v>19</v>
       </c>
       <c r="E139">
-        <v>0.06829600071127136</v>
+        <v>0.06829600071127123</v>
       </c>
       <c r="F139">
         <v>0.001091703056768559</v>
@@ -7041,7 +7041,7 @@
         <v>48</v>
       </c>
       <c r="L139">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M139">
         <v>101</v>
@@ -7068,7 +7068,7 @@
         <v>19</v>
       </c>
       <c r="E140">
-        <v>0.06829600071127127</v>
+        <v>0.06829600071127123</v>
       </c>
       <c r="F140">
         <v>0.001091703056768559</v>
@@ -7089,7 +7089,7 @@
         <v>48</v>
       </c>
       <c r="L140">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M140">
         <v>101</v>
@@ -7116,7 +7116,7 @@
         <v>5</v>
       </c>
       <c r="E141">
-        <v>0.009250173780115421</v>
+        <v>0.009250173780115412</v>
       </c>
       <c r="F141">
         <v>0.0008680555555555555</v>
@@ -7137,7 +7137,7 @@
         <v>62</v>
       </c>
       <c r="L141">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="M141">
         <v>227</v>
@@ -7185,7 +7185,7 @@
         <v>63</v>
       </c>
       <c r="L142">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M142">
         <v>202</v>
@@ -7212,7 +7212,7 @@
         <v>3</v>
       </c>
       <c r="E143">
-        <v>0.008110103308476361</v>
+        <v>0.008110103308476342</v>
       </c>
       <c r="F143">
         <v>0.0009000900090009001</v>
@@ -7233,7 +7233,7 @@
         <v>64</v>
       </c>
       <c r="L143">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="M143">
         <v>218</v>
@@ -7260,7 +7260,7 @@
         <v>18</v>
       </c>
       <c r="E144">
-        <v>0.06678398361297724</v>
+        <v>0.06678398361297715</v>
       </c>
       <c r="F144">
         <v>0.001047120418848168</v>
@@ -7281,7 +7281,7 @@
         <v>49</v>
       </c>
       <c r="L144">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M144">
         <v>130</v>
@@ -7308,7 +7308,7 @@
         <v>6</v>
       </c>
       <c r="E145">
-        <v>0.007653380926048058</v>
+        <v>0.007653380926048066</v>
       </c>
       <c r="F145">
         <v>0.0008032128514056225</v>
@@ -7329,7 +7329,7 @@
         <v>61</v>
       </c>
       <c r="L145">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="M145">
         <v>242</v>
@@ -7356,7 +7356,7 @@
         <v>19</v>
       </c>
       <c r="E146">
-        <v>0.04099856945643321</v>
+        <v>0.04099856945643323</v>
       </c>
       <c r="F146">
         <v>0.001020408163265306</v>
@@ -7377,7 +7377,7 @@
         <v>48</v>
       </c>
       <c r="L146">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M146">
         <v>148</v>
@@ -7404,7 +7404,7 @@
         <v>35</v>
       </c>
       <c r="E147">
-        <v>0.1310564445761887</v>
+        <v>0.1310564445761886</v>
       </c>
       <c r="F147">
         <v>0.001136363636363636</v>
@@ -7452,7 +7452,7 @@
         <v>14</v>
       </c>
       <c r="E148">
-        <v>0.06044405859870453</v>
+        <v>0.06044405859870446</v>
       </c>
       <c r="F148">
         <v>0.001029866117404737</v>
@@ -7548,7 +7548,7 @@
         <v>35</v>
       </c>
       <c r="E150">
-        <v>0.3310001912524271</v>
+        <v>0.3310001912524273</v>
       </c>
       <c r="F150">
         <v>0.001207729468599034</v>
@@ -7596,7 +7596,7 @@
         <v>17</v>
       </c>
       <c r="E151">
-        <v>0.1963511396066271</v>
+        <v>0.1963511396066273</v>
       </c>
       <c r="F151">
         <v>0.001098901098901099</v>
@@ -7644,7 +7644,7 @@
         <v>33</v>
       </c>
       <c r="E152">
-        <v>0.2329380286125921</v>
+        <v>0.2329380286125919</v>
       </c>
       <c r="F152">
         <v>0.001233045622688039</v>
@@ -7692,7 +7692,7 @@
         <v>23</v>
       </c>
       <c r="E153">
-        <v>0.07920250839922402</v>
+        <v>0.07920250839922391</v>
       </c>
       <c r="F153">
         <v>0.001104972375690608</v>
@@ -7713,7 +7713,7 @@
         <v>44</v>
       </c>
       <c r="L153">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M153">
         <v>93</v>
@@ -7740,7 +7740,7 @@
         <v>16</v>
       </c>
       <c r="E154">
-        <v>0.1388177419004028</v>
+        <v>0.138817741900403</v>
       </c>
       <c r="F154">
         <v>0.001003009027081244</v>
@@ -7788,7 +7788,7 @@
         <v>73</v>
       </c>
       <c r="E155">
-        <v>0.8221990144099689</v>
+        <v>0.8221990144099691</v>
       </c>
       <c r="F155">
         <v>0.0012531328320802</v>
@@ -7836,7 +7836,7 @@
         <v>34</v>
       </c>
       <c r="E156">
-        <v>0.368298097241721</v>
+        <v>0.3682980972417211</v>
       </c>
       <c r="F156">
         <v>0.001123595505617978</v>
@@ -7884,7 +7884,7 @@
         <v>25</v>
       </c>
       <c r="E157">
-        <v>0.1248677914582099</v>
+        <v>0.1248677914582098</v>
       </c>
       <c r="F157">
         <v>0.001123595505617978</v>
@@ -7932,7 +7932,7 @@
         <v>53</v>
       </c>
       <c r="E158">
-        <v>0.7552465335439326</v>
+        <v>0.7552465335439329</v>
       </c>
       <c r="F158">
         <v>0.001225490196078431</v>
@@ -7980,7 +7980,7 @@
         <v>10</v>
       </c>
       <c r="E159">
-        <v>0.03098946147202334</v>
+        <v>0.03098946147202333</v>
       </c>
       <c r="F159">
         <v>0.0009775171065493646</v>
@@ -8001,7 +8001,7 @@
         <v>57</v>
       </c>
       <c r="L159">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M159">
         <v>176</v>
@@ -8028,7 +8028,7 @@
         <v>15</v>
       </c>
       <c r="E160">
-        <v>0.04333893199557709</v>
+        <v>0.04333893199557708</v>
       </c>
       <c r="F160">
         <v>0.001023541453428864</v>
@@ -8049,7 +8049,7 @@
         <v>52</v>
       </c>
       <c r="L160">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M160">
         <v>145</v>
@@ -8076,7 +8076,7 @@
         <v>35</v>
       </c>
       <c r="E161">
-        <v>0.1890650853527082</v>
+        <v>0.1890650853527084</v>
       </c>
       <c r="F161">
         <v>0.001226993865030675</v>
@@ -8124,7 +8124,7 @@
         <v>10</v>
       </c>
       <c r="E162">
-        <v>0.05041570705159135</v>
+        <v>0.05041570705159137</v>
       </c>
       <c r="F162">
         <v>0.0009615384615384616</v>
@@ -8172,7 +8172,7 @@
         <v>15</v>
       </c>
       <c r="E163">
-        <v>0.09797849072511557</v>
+        <v>0.09797849072511552</v>
       </c>
       <c r="F163">
         <v>0.001106194690265487</v>
@@ -8193,7 +8193,7 @@
         <v>52</v>
       </c>
       <c r="L163">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M163">
         <v>92</v>
@@ -8220,7 +8220,7 @@
         <v>6</v>
       </c>
       <c r="E164">
-        <v>0.02933380421366982</v>
+        <v>0.02933380421366986</v>
       </c>
       <c r="F164">
         <v>0.0009852216748768472</v>
@@ -8241,7 +8241,7 @@
         <v>61</v>
       </c>
       <c r="L164">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M164">
         <v>172</v>
@@ -8268,7 +8268,7 @@
         <v>3</v>
       </c>
       <c r="E165">
-        <v>0.005543495864485808</v>
+        <v>0.00554349586448581</v>
       </c>
       <c r="F165">
         <v>0.0008695652173913044</v>
@@ -8289,7 +8289,7 @@
         <v>64</v>
       </c>
       <c r="L165">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="M165">
         <v>226</v>
@@ -8316,7 +8316,7 @@
         <v>10</v>
       </c>
       <c r="E166">
-        <v>0.03047527208344222</v>
+        <v>0.03047527208344217</v>
       </c>
       <c r="F166">
         <v>0.0009794319294809011</v>
@@ -8337,7 +8337,7 @@
         <v>57</v>
       </c>
       <c r="L166">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M166">
         <v>174</v>
@@ -8385,7 +8385,7 @@
         <v>53</v>
       </c>
       <c r="L167">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M167">
         <v>150</v>
@@ -8412,7 +8412,7 @@
         <v>10</v>
       </c>
       <c r="E168">
-        <v>0.03406801842552082</v>
+        <v>0.03406801842552083</v>
       </c>
       <c r="F168">
         <v>0.0009416195856873823</v>
@@ -8433,7 +8433,7 @@
         <v>57</v>
       </c>
       <c r="L168">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M168">
         <v>197</v>
@@ -8460,7 +8460,7 @@
         <v>15</v>
       </c>
       <c r="E169">
-        <v>0.07945951727324818</v>
+        <v>0.07945951727324824</v>
       </c>
       <c r="F169">
         <v>0.001067235859124867</v>
@@ -8481,7 +8481,7 @@
         <v>52</v>
       </c>
       <c r="L169">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M169">
         <v>115</v>
@@ -8508,7 +8508,7 @@
         <v>24</v>
       </c>
       <c r="E170">
-        <v>0.1553630173803937</v>
+        <v>0.1553630173803936</v>
       </c>
       <c r="F170">
         <v>0.001162790697674419</v>
@@ -8556,7 +8556,7 @@
         <v>24</v>
       </c>
       <c r="E171">
-        <v>0.1553630173803937</v>
+        <v>0.1553630173803936</v>
       </c>
       <c r="F171">
         <v>0.001162790697674419</v>
@@ -8604,7 +8604,7 @@
         <v>2</v>
       </c>
       <c r="E172">
-        <v>0.007842644110574759</v>
+        <v>0.007842644110574752</v>
       </c>
       <c r="F172">
         <v>0.0008071025020177562</v>
@@ -8625,7 +8625,7 @@
         <v>65</v>
       </c>
       <c r="L172">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="M172">
         <v>241</v>
@@ -8652,7 +8652,7 @@
         <v>10</v>
       </c>
       <c r="E173">
-        <v>0.1366871801774922</v>
+        <v>0.1366871801774923</v>
       </c>
       <c r="F173">
         <v>0.0009832841691248771</v>
@@ -8700,7 +8700,7 @@
         <v>11</v>
       </c>
       <c r="E174">
-        <v>0.05965529116877549</v>
+        <v>0.05965529116877551</v>
       </c>
       <c r="F174">
         <v>0.001085776330076004</v>
@@ -8748,7 +8748,7 @@
         <v>57</v>
       </c>
       <c r="E175">
-        <v>0.6416594465509463</v>
+        <v>0.6416594465509465</v>
       </c>
       <c r="F175">
         <v>0.001338688085676037</v>
@@ -8796,7 +8796,7 @@
         <v>27</v>
       </c>
       <c r="E176">
-        <v>0.3423251801581169</v>
+        <v>0.342325180158117</v>
       </c>
       <c r="F176">
         <v>0.00116144018583043</v>
@@ -8844,7 +8844,7 @@
         <v>9</v>
       </c>
       <c r="E177">
-        <v>0.05153384163896473</v>
+        <v>0.05153384163896475</v>
       </c>
       <c r="F177">
         <v>0.0009372071227741331</v>
@@ -8892,7 +8892,7 @@
         <v>13</v>
       </c>
       <c r="E178">
-        <v>0.02406951715436392</v>
+        <v>0.0240695171543639</v>
       </c>
       <c r="F178">
         <v>0.0009389671361502347</v>
@@ -8913,7 +8913,7 @@
         <v>54</v>
       </c>
       <c r="L178">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M178">
         <v>199</v>
@@ -8940,7 +8940,7 @@
         <v>11</v>
       </c>
       <c r="E179">
-        <v>0.110724896227415</v>
+        <v>0.1107248962274153</v>
       </c>
       <c r="F179">
         <v>0.001006036217303823</v>
@@ -8988,7 +8988,7 @@
         <v>20</v>
       </c>
       <c r="E180">
-        <v>0.09873524586416121</v>
+        <v>0.0987352458641612</v>
       </c>
       <c r="F180">
         <v>0.00112739571589628</v>
@@ -9009,7 +9009,7 @@
         <v>47</v>
       </c>
       <c r="L180">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M180">
         <v>81</v>
@@ -9036,7 +9036,7 @@
         <v>6</v>
       </c>
       <c r="E181">
-        <v>0.01862047699818122</v>
+        <v>0.0186204769981812</v>
       </c>
       <c r="F181">
         <v>0.0009354536950420954</v>
@@ -9057,7 +9057,7 @@
         <v>61</v>
       </c>
       <c r="L181">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M181">
         <v>201</v>
@@ -9084,7 +9084,7 @@
         <v>8</v>
       </c>
       <c r="E182">
-        <v>0.03548438891963195</v>
+        <v>0.03548438891963197</v>
       </c>
       <c r="F182">
         <v>0.000992063492063492</v>
@@ -9105,7 +9105,7 @@
         <v>59</v>
       </c>
       <c r="L182">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M182">
         <v>169</v>
@@ -9132,7 +9132,7 @@
         <v>7</v>
       </c>
       <c r="E183">
-        <v>0.04316518350962378</v>
+        <v>0.04316518350962385</v>
       </c>
       <c r="F183">
         <v>0.0009784735812133072</v>
@@ -9153,7 +9153,7 @@
         <v>60</v>
       </c>
       <c r="L183">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M183">
         <v>175</v>
@@ -9180,7 +9180,7 @@
         <v>21</v>
       </c>
       <c r="E184">
-        <v>0.1649015933569542</v>
+        <v>0.1649015933569543</v>
       </c>
       <c r="F184">
         <v>0.001146788990825688</v>
@@ -9249,7 +9249,7 @@
         <v>58</v>
       </c>
       <c r="L185">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M185">
         <v>178</v>
@@ -9276,7 +9276,7 @@
         <v>11</v>
       </c>
       <c r="E186">
-        <v>0.02619460588570609</v>
+        <v>0.0261946058857061</v>
       </c>
       <c r="F186">
         <v>0.0009624639076034649</v>
@@ -9297,7 +9297,7 @@
         <v>56</v>
       </c>
       <c r="L186">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M186">
         <v>185</v>
@@ -9324,7 +9324,7 @@
         <v>12</v>
       </c>
       <c r="E187">
-        <v>0.04575718734768931</v>
+        <v>0.04575718734768928</v>
       </c>
       <c r="F187">
         <v>0.001023541453428864</v>
@@ -9345,7 +9345,7 @@
         <v>55</v>
       </c>
       <c r="L187">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="M187">
         <v>145</v>
@@ -9372,7 +9372,7 @@
         <v>34</v>
       </c>
       <c r="E188">
-        <v>0.2937851196929068</v>
+        <v>0.2937851196929069</v>
       </c>
       <c r="F188">
         <v>0.001203369434416366</v>
@@ -9468,7 +9468,7 @@
         <v>13</v>
       </c>
       <c r="E190">
-        <v>0.06631161295112521</v>
+        <v>0.06631161295112518</v>
       </c>
       <c r="F190">
         <v>0.000975609756097561</v>
@@ -9489,7 +9489,7 @@
         <v>54</v>
       </c>
       <c r="L190">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M190">
         <v>177</v>
@@ -9516,7 +9516,7 @@
         <v>6</v>
       </c>
       <c r="E191">
-        <v>0.02733760406022359</v>
+        <v>0.02733760406022355</v>
       </c>
       <c r="F191">
         <v>0.001012145748987854</v>
@@ -9537,7 +9537,7 @@
         <v>61</v>
       </c>
       <c r="L191">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="M191">
         <v>154</v>
@@ -9564,7 +9564,7 @@
         <v>14</v>
       </c>
       <c r="E192">
-        <v>0.06927609462288721</v>
+        <v>0.06927609462288714</v>
       </c>
       <c r="F192">
         <v>0.001024590163934426</v>
@@ -9585,7 +9585,7 @@
         <v>53</v>
       </c>
       <c r="L192">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M192">
         <v>144</v>
@@ -9660,7 +9660,7 @@
         <v>14</v>
       </c>
       <c r="E194">
-        <v>0.06927609462288721</v>
+        <v>0.06927609462288715</v>
       </c>
       <c r="F194">
         <v>0.001024590163934426</v>
@@ -9681,7 +9681,7 @@
         <v>53</v>
       </c>
       <c r="L194">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M194">
         <v>144</v>
@@ -9708,7 +9708,7 @@
         <v>5</v>
       </c>
       <c r="E195">
-        <v>0.01161294882901369</v>
+        <v>0.0116129488290137</v>
       </c>
       <c r="F195">
         <v>0.0008960573476702509</v>
@@ -9729,7 +9729,7 @@
         <v>62</v>
       </c>
       <c r="L195">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="M195">
         <v>220</v>
@@ -9756,7 +9756,7 @@
         <v>4</v>
       </c>
       <c r="E196">
-        <v>0.003335881316269054</v>
+        <v>0.003335881316269059</v>
       </c>
       <c r="F196">
         <v>0.0008244023083264633</v>
@@ -9777,7 +9777,7 @@
         <v>63</v>
       </c>
       <c r="L196">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="M196">
         <v>237</v>
@@ -9825,7 +9825,7 @@
         <v>62</v>
       </c>
       <c r="L197">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="M197">
         <v>232</v>
@@ -9852,7 +9852,7 @@
         <v>5</v>
       </c>
       <c r="E198">
-        <v>0.009852611023087481</v>
+        <v>0.009852611023087491</v>
       </c>
       <c r="F198">
         <v>0.0008481764206955047</v>
@@ -9873,7 +9873,7 @@
         <v>62</v>
       </c>
       <c r="L198">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M198">
         <v>232</v>
@@ -9948,7 +9948,7 @@
         <v>6</v>
       </c>
       <c r="E200">
-        <v>0.0410343411055221</v>
+        <v>0.04103434110552209</v>
       </c>
       <c r="F200">
         <v>0.000968054211035818</v>
@@ -9969,7 +9969,7 @@
         <v>61</v>
       </c>
       <c r="L200">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M200">
         <v>182</v>
@@ -9996,7 +9996,7 @@
         <v>9</v>
       </c>
       <c r="E201">
-        <v>0.07410758023573481</v>
+        <v>0.0741075802357348</v>
       </c>
       <c r="F201">
         <v>0.001041666666666667</v>
@@ -10017,7 +10017,7 @@
         <v>58</v>
       </c>
       <c r="L201">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M201">
         <v>133</v>
@@ -10044,7 +10044,7 @@
         <v>23</v>
       </c>
       <c r="E202">
-        <v>0.1011674952657496</v>
+        <v>0.1011674952657495</v>
       </c>
       <c r="F202">
         <v>0.001089324618736384</v>
@@ -10092,7 +10092,7 @@
         <v>26</v>
       </c>
       <c r="E203">
-        <v>0.1415394595681426</v>
+        <v>0.1415394595681425</v>
       </c>
       <c r="F203">
         <v>0.001153402537485583</v>
@@ -10140,7 +10140,7 @@
         <v>47</v>
       </c>
       <c r="E204">
-        <v>0.6785881267284747</v>
+        <v>0.6785881267284749</v>
       </c>
       <c r="F204">
         <v>0.001187648456057007</v>
@@ -10188,7 +10188,7 @@
         <v>7</v>
       </c>
       <c r="E205">
-        <v>0.04019809686723545</v>
+        <v>0.04019809686723542</v>
       </c>
       <c r="F205">
         <v>0.001031991744066047</v>
@@ -10209,7 +10209,7 @@
         <v>60</v>
       </c>
       <c r="L205">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M205">
         <v>139</v>
@@ -10236,7 +10236,7 @@
         <v>3</v>
       </c>
       <c r="E206">
-        <v>0.00640426724486774</v>
+        <v>0.006404267244867728</v>
       </c>
       <c r="F206">
         <v>0.0008849557522123894</v>
@@ -10257,7 +10257,7 @@
         <v>64</v>
       </c>
       <c r="L206">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="M206">
         <v>224</v>
@@ -10305,7 +10305,7 @@
         <v>60</v>
       </c>
       <c r="L207">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M207">
         <v>183</v>
@@ -10332,7 +10332,7 @@
         <v>23</v>
       </c>
       <c r="E208">
-        <v>0.2763427773694669</v>
+        <v>0.2763427773694672</v>
       </c>
       <c r="F208">
         <v>0.001023541453428864</v>
@@ -10380,7 +10380,7 @@
         <v>5</v>
       </c>
       <c r="E209">
-        <v>0.04632669530217724</v>
+        <v>0.04632669530217727</v>
       </c>
       <c r="F209">
         <v>0.0009216589861751152</v>
@@ -10401,7 +10401,7 @@
         <v>62</v>
       </c>
       <c r="L209">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="M209">
         <v>208</v>
@@ -10449,7 +10449,7 @@
         <v>62</v>
       </c>
       <c r="L210">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="M210">
         <v>221</v>
@@ -10476,7 +10476,7 @@
         <v>3</v>
       </c>
       <c r="E211">
-        <v>0.01943935886733587</v>
+        <v>0.01943935886733585</v>
       </c>
       <c r="F211">
         <v>0.0009541984732824427</v>
@@ -10497,7 +10497,7 @@
         <v>64</v>
       </c>
       <c r="L211">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="M211">
         <v>189</v>
@@ -10620,7 +10620,7 @@
         <v>49</v>
       </c>
       <c r="E214">
-        <v>0.6888503275092158</v>
+        <v>0.6888503275092164</v>
       </c>
       <c r="F214">
         <v>0.001236093943139679</v>
@@ -10668,7 +10668,7 @@
         <v>11</v>
       </c>
       <c r="E215">
-        <v>0.04315486197212738</v>
+        <v>0.04315486197212729</v>
       </c>
       <c r="F215">
         <v>0.001038421599169263</v>
@@ -10689,7 +10689,7 @@
         <v>56</v>
       </c>
       <c r="L215">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M215">
         <v>135</v>
@@ -10716,7 +10716,7 @@
         <v>47</v>
       </c>
       <c r="E216">
-        <v>0.7153946698921541</v>
+        <v>0.7153946698921548</v>
       </c>
       <c r="F216">
         <v>0.001277139208173691</v>
@@ -10764,7 +10764,7 @@
         <v>21</v>
       </c>
       <c r="E217">
-        <v>0.06880780320530726</v>
+        <v>0.06880780320530724</v>
       </c>
       <c r="F217">
         <v>0.001074113856068743</v>
@@ -10785,7 +10785,7 @@
         <v>46</v>
       </c>
       <c r="L217">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M217">
         <v>112</v>
@@ -10812,7 +10812,7 @@
         <v>4</v>
       </c>
       <c r="E218">
-        <v>0.0282893859633095</v>
+        <v>0.02828938596330946</v>
       </c>
       <c r="F218">
         <v>0.0009523809523809524</v>
@@ -10833,7 +10833,7 @@
         <v>63</v>
       </c>
       <c r="L218">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M218">
         <v>191</v>
@@ -10860,7 +10860,7 @@
         <v>5</v>
       </c>
       <c r="E219">
-        <v>0.02485434344736211</v>
+        <v>0.02485434344736214</v>
       </c>
       <c r="F219">
         <v>0.0009140767824497258</v>
@@ -10881,7 +10881,7 @@
         <v>62</v>
       </c>
       <c r="L219">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="M219">
         <v>212</v>
@@ -10908,7 +10908,7 @@
         <v>23</v>
       </c>
       <c r="E220">
-        <v>0.09163312078917783</v>
+        <v>0.09163312078917776</v>
       </c>
       <c r="F220">
         <v>0.001111111111111111</v>
@@ -10929,7 +10929,7 @@
         <v>44</v>
       </c>
       <c r="L220">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M220">
         <v>89</v>
@@ -10956,7 +10956,7 @@
         <v>9</v>
       </c>
       <c r="E221">
-        <v>0.01516842831533816</v>
+        <v>0.01516842831533818</v>
       </c>
       <c r="F221">
         <v>0.0009033423667570009</v>
@@ -10977,7 +10977,7 @@
         <v>58</v>
       </c>
       <c r="L221">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="M221">
         <v>216</v>
@@ -11004,7 +11004,7 @@
         <v>30</v>
       </c>
       <c r="E222">
-        <v>0.09890784924036376</v>
+        <v>0.09890784924036355</v>
       </c>
       <c r="F222">
         <v>0.00112739571589628</v>
@@ -11025,7 +11025,7 @@
         <v>37</v>
       </c>
       <c r="L222">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M222">
         <v>81</v>
@@ -11052,7 +11052,7 @@
         <v>18</v>
       </c>
       <c r="E223">
-        <v>0.0484520336877764</v>
+        <v>0.04845203368777638</v>
       </c>
       <c r="F223">
         <v>0.001020408163265306</v>
@@ -11073,7 +11073,7 @@
         <v>49</v>
       </c>
       <c r="L223">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="M223">
         <v>148</v>
@@ -11100,7 +11100,7 @@
         <v>7</v>
       </c>
       <c r="E224">
-        <v>0.01248965526181808</v>
+        <v>0.01248965526181807</v>
       </c>
       <c r="F224">
         <v>0.0008968609865470852</v>
@@ -11121,7 +11121,7 @@
         <v>60</v>
       </c>
       <c r="L224">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="M224">
         <v>219</v>
@@ -11148,7 +11148,7 @@
         <v>8</v>
       </c>
       <c r="E225">
-        <v>0.02134632461765695</v>
+        <v>0.02134632461765694</v>
       </c>
       <c r="F225">
         <v>0.000925925925925926</v>
@@ -11169,7 +11169,7 @@
         <v>59</v>
       </c>
       <c r="L225">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M225">
         <v>207</v>
@@ -11196,7 +11196,7 @@
         <v>10</v>
       </c>
       <c r="E226">
-        <v>0.05443297480293963</v>
+        <v>0.05443297480293962</v>
       </c>
       <c r="F226">
         <v>0.0009950248756218905</v>
@@ -11265,7 +11265,7 @@
         <v>59</v>
       </c>
       <c r="L227">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="M227">
         <v>207</v>
@@ -11292,7 +11292,7 @@
         <v>28</v>
       </c>
       <c r="E228">
-        <v>0.125875141088382</v>
+        <v>0.1258751410883819</v>
       </c>
       <c r="F228">
         <v>0.001146788990825688</v>
@@ -11388,7 +11388,7 @@
         <v>26</v>
       </c>
       <c r="E230">
-        <v>0.1343150297085475</v>
+        <v>0.1343150297085474</v>
       </c>
       <c r="F230">
         <v>0.00117096018735363</v>
@@ -11436,7 +11436,7 @@
         <v>33</v>
       </c>
       <c r="E231">
-        <v>0.2051598147258404</v>
+        <v>0.2051598147258405</v>
       </c>
       <c r="F231">
         <v>0.001237623762376238</v>
@@ -11484,7 +11484,7 @@
         <v>27</v>
       </c>
       <c r="E232">
-        <v>0.2299126173318285</v>
+        <v>0.2299126173318284</v>
       </c>
       <c r="F232">
         <v>0.001194743130227001</v>
@@ -11532,7 +11532,7 @@
         <v>50</v>
       </c>
       <c r="E233">
-        <v>0.7216121082811184</v>
+        <v>0.7216121082811188</v>
       </c>
       <c r="F233">
         <v>0.001251564455569462</v>
@@ -11580,7 +11580,7 @@
         <v>7</v>
       </c>
       <c r="E234">
-        <v>0.05623067174548649</v>
+        <v>0.05623067174548652</v>
       </c>
       <c r="F234">
         <v>0.001034126163391934</v>
@@ -11628,7 +11628,7 @@
         <v>8</v>
       </c>
       <c r="E235">
-        <v>0.03675683616064056</v>
+        <v>0.03675683616064054</v>
       </c>
       <c r="F235">
         <v>0.0009930486593843098</v>
@@ -11649,7 +11649,7 @@
         <v>59</v>
       </c>
       <c r="L235">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="M235">
         <v>168</v>
@@ -11676,7 +11676,7 @@
         <v>14</v>
       </c>
       <c r="E236">
-        <v>0.07236131059049185</v>
+        <v>0.07236131059049174</v>
       </c>
       <c r="F236">
         <v>0.001095290251916758</v>
@@ -11697,7 +11697,7 @@
         <v>53</v>
       </c>
       <c r="L236">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M236">
         <v>100</v>
@@ -11724,7 +11724,7 @@
         <v>9</v>
       </c>
       <c r="E237">
-        <v>0.1197288025264075</v>
+        <v>0.1197288025264077</v>
       </c>
       <c r="F237">
         <v>0.000975609756097561</v>
@@ -11772,7 +11772,7 @@
         <v>51</v>
       </c>
       <c r="E238">
-        <v>0.7283769952362558</v>
+        <v>0.7283769952362561</v>
       </c>
       <c r="F238">
         <v>0.001297016861219196</v>
@@ -11820,7 +11820,7 @@
         <v>24</v>
       </c>
       <c r="E239">
-        <v>0.0937334127533129</v>
+        <v>0.0937334127533128</v>
       </c>
       <c r="F239">
         <v>0.001112347052280311</v>
@@ -11841,7 +11841,7 @@
         <v>43</v>
       </c>
       <c r="L239">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M239">
         <v>88</v>
@@ -11868,7 +11868,7 @@
         <v>9</v>
       </c>
       <c r="E240">
-        <v>0.02272859508644209</v>
+        <v>0.02272859508644208</v>
       </c>
       <c r="F240">
         <v>0.0009276437847866419</v>
@@ -11889,7 +11889,7 @@
         <v>58</v>
       </c>
       <c r="L240">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M240">
         <v>206</v>
@@ -11916,7 +11916,7 @@
         <v>22</v>
       </c>
       <c r="E241">
-        <v>0.07995656027706263</v>
+        <v>0.07995656027706248</v>
       </c>
       <c r="F241">
         <v>0.001096491228070175</v>
@@ -11937,7 +11937,7 @@
         <v>45</v>
       </c>
       <c r="L241">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M241">
         <v>99</v>
@@ -11964,7 +11964,7 @@
         <v>33</v>
       </c>
       <c r="E242">
-        <v>0.1414793597702305</v>
+        <v>0.1414793597702304</v>
       </c>
       <c r="F242">
         <v>0.001183431952662722</v>
@@ -12012,7 +12012,7 @@
         <v>14</v>
       </c>
       <c r="E243">
-        <v>0.1293363176298777</v>
+        <v>0.1293363176298779</v>
       </c>
       <c r="F243">
         <v>0.001052631578947368</v>
@@ -12060,7 +12060,7 @@
         <v>3</v>
       </c>
       <c r="E244">
-        <v>0.03673802099461343</v>
+        <v>0.03673802099461344</v>
       </c>
       <c r="F244">
         <v>0.0008525149190110827</v>
@@ -12081,7 +12081,7 @@
         <v>64</v>
       </c>
       <c r="L244">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M244">
         <v>231</v>
@@ -12129,7 +12129,7 @@
         <v>64</v>
       </c>
       <c r="L245">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="M245">
         <v>194</v>
@@ -12156,7 +12156,7 @@
         <v>27</v>
       </c>
       <c r="E246">
-        <v>0.2646097868348309</v>
+        <v>0.2646097868348311</v>
       </c>
       <c r="F246">
         <v>0.001076426264800861</v>
@@ -12204,7 +12204,7 @@
         <v>17</v>
       </c>
       <c r="E247">
-        <v>0.08384844457439949</v>
+        <v>0.08384844457439948</v>
       </c>
       <c r="F247">
         <v>0.001015228426395939</v>
@@ -12225,7 +12225,7 @@
         <v>50</v>
       </c>
       <c r="L247">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M247">
         <v>152</v>
@@ -12252,7 +12252,7 @@
         <v>14</v>
       </c>
       <c r="E248">
-        <v>0.1689652195296816</v>
+        <v>0.1689652195296818</v>
       </c>
       <c r="F248">
         <v>0.001007049345417925</v>
@@ -12300,7 +12300,7 @@
         <v>23</v>
       </c>
       <c r="E249">
-        <v>0.3225143031638126</v>
+        <v>0.3225143031638129</v>
       </c>
       <c r="F249">
         <v>0.001081081081081081</v>
@@ -12348,7 +12348,7 @@
         <v>23</v>
       </c>
       <c r="E250">
-        <v>0.1420656855525038</v>
+        <v>0.1420656855525037</v>
       </c>
       <c r="F250">
         <v>0.001146788990825688</v>
@@ -12396,7 +12396,7 @@
         <v>1</v>
       </c>
       <c r="E251">
-        <v>0.02059456654017108</v>
+        <v>0.0205945665401711</v>
       </c>
       <c r="F251">
         <v>0.0008445945945945946</v>
@@ -12417,7 +12417,7 @@
         <v>66</v>
       </c>
       <c r="L251">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="M251">
         <v>233</v>
@@ -12444,7 +12444,7 @@
         <v>25</v>
       </c>
       <c r="E252">
-        <v>0.09829046056665373</v>
+        <v>0.09829046056665382</v>
       </c>
       <c r="F252">
         <v>0.001137656427758817</v>
@@ -12465,7 +12465,7 @@
         <v>42</v>
       </c>
       <c r="L252">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M252">
         <v>74</v>
@@ -12492,7 +12492,7 @@
         <v>13</v>
       </c>
       <c r="E253">
-        <v>0.05614791017866327</v>
+        <v>0.05614791017866318</v>
       </c>
       <c r="F253">
         <v>0.001006036217303823</v>
@@ -12540,7 +12540,7 @@
         <v>2</v>
       </c>
       <c r="E254">
-        <v>0.004340929190219014</v>
+        <v>0.004340929190219008</v>
       </c>
       <c r="F254">
         <v>0.0008097165991902834</v>
@@ -12561,7 +12561,7 @@
         <v>65</v>
       </c>
       <c r="L254">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="M254">
         <v>240</v>
@@ -12588,7 +12588,7 @@
         <v>19</v>
       </c>
       <c r="E255">
-        <v>0.05423115011936077</v>
+        <v>0.0542311501193608</v>
       </c>
       <c r="F255">
         <v>0.001027749229188078</v>
@@ -12636,7 +12636,7 @@
         <v>12</v>
       </c>
       <c r="E256">
-        <v>0.09667574350587992</v>
+        <v>0.09667574350587986</v>
       </c>
       <c r="F256">
         <v>0.001089324618736384</v>
@@ -12684,7 +12684,7 @@
         <v>48</v>
       </c>
       <c r="E257">
-        <v>0.4379209815737334</v>
+        <v>0.4379209815737333</v>
       </c>
       <c r="F257">
         <v>0.001291989664082687</v>
@@ -12732,7 +12732,7 @@
         <v>9</v>
       </c>
       <c r="E258">
-        <v>0.03822553571129245</v>
+        <v>0.0382255357112924</v>
       </c>
       <c r="F258">
         <v>0.00101419878296146</v>
@@ -12753,7 +12753,7 @@
         <v>58</v>
       </c>
       <c r="L258">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M258">
         <v>153</v>
@@ -12780,7 +12780,7 @@
         <v>50</v>
       </c>
       <c r="E259">
-        <v>0.7047885052760353</v>
+        <v>0.7047885052760361</v>
       </c>
       <c r="F259">
         <v>0.001194743130227001</v>
@@ -12828,7 +12828,7 @@
         <v>21</v>
       </c>
       <c r="E260">
-        <v>0.08255583358230169</v>
+        <v>0.0825558335823016</v>
       </c>
       <c r="F260">
         <v>0.001095290251916758</v>
@@ -12849,7 +12849,7 @@
         <v>46</v>
       </c>
       <c r="L260">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="M260">
         <v>100</v>
@@ -12876,7 +12876,7 @@
         <v>11</v>
       </c>
       <c r="E261">
-        <v>0.08021255918029244</v>
+        <v>0.08021255918029245</v>
       </c>
       <c r="F261">
         <v>0.001064962726304579</v>
@@ -12897,7 +12897,7 @@
         <v>56</v>
       </c>
       <c r="L261">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M261">
         <v>117</v>
@@ -12924,7 +12924,7 @@
         <v>3</v>
       </c>
       <c r="E262">
-        <v>0.003569379924706341</v>
+        <v>0.003569379924706342</v>
       </c>
       <c r="F262">
         <v>0.0008103727714748784</v>
@@ -12945,7 +12945,7 @@
         <v>64</v>
       </c>
       <c r="L262">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="M262">
         <v>239</v>
@@ -13068,7 +13068,7 @@
         <v>8</v>
       </c>
       <c r="E265">
-        <v>0.05268150620552994</v>
+        <v>0.05268150620552992</v>
       </c>
       <c r="F265">
         <v>0.001064962726304579</v>
@@ -13116,7 +13116,7 @@
         <v>58</v>
       </c>
       <c r="E266">
-        <v>0.454801568613359</v>
+        <v>0.4548015686133591</v>
       </c>
       <c r="F266">
         <v>0.001345895020188425</v>
@@ -13164,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="E267">
-        <v>0.07689697360159459</v>
+        <v>0.07689697360159456</v>
       </c>
       <c r="F267">
         <v>0.001050420168067227</v>
@@ -13185,7 +13185,7 @@
         <v>51</v>
       </c>
       <c r="L267">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="M267">
         <v>127</v>
@@ -13212,7 +13212,7 @@
         <v>9</v>
       </c>
       <c r="E268">
-        <v>0.01327000812050968</v>
+        <v>0.01327000812050967</v>
       </c>
       <c r="F268">
         <v>0.0009276437847866419</v>
@@ -13233,7 +13233,7 @@
         <v>58</v>
       </c>
       <c r="L268">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M268">
         <v>206</v>
@@ -13260,7 +13260,7 @@
         <v>12</v>
       </c>
       <c r="E269">
-        <v>0.04050331434560482</v>
+        <v>0.04050331434560481</v>
       </c>
       <c r="F269">
         <v>0.0009871668311944718</v>
@@ -13281,7 +13281,7 @@
         <v>55</v>
       </c>
       <c r="L269">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M269">
         <v>171</v>
@@ -13308,7 +13308,7 @@
         <v>8</v>
       </c>
       <c r="E270">
-        <v>0.03311548476597759</v>
+        <v>0.03311548476597762</v>
       </c>
       <c r="F270">
         <v>0.0009433962264150943</v>
@@ -13329,7 +13329,7 @@
         <v>59</v>
       </c>
       <c r="L270">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="M270">
         <v>196</v>
@@ -13404,7 +13404,7 @@
         <v>19</v>
       </c>
       <c r="E272">
-        <v>0.1383847196306715</v>
+        <v>0.1383847196306714</v>
       </c>
       <c r="F272">
         <v>0.001135073779795687</v>
@@ -13452,7 +13452,7 @@
         <v>11</v>
       </c>
       <c r="E273">
-        <v>0.05598947601344478</v>
+        <v>0.05598947601344476</v>
       </c>
       <c r="F273">
         <v>0.001044932079414838</v>
@@ -13500,7 +13500,7 @@
         <v>3</v>
       </c>
       <c r="E274">
-        <v>0.003224055950306047</v>
+        <v>0.003224055950306037</v>
       </c>
       <c r="F274">
         <v>0.0008210180623973727</v>
@@ -13521,7 +13521,7 @@
         <v>64</v>
       </c>
       <c r="L274">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="M274">
         <v>238</v>
@@ -13548,7 +13548,7 @@
         <v>8</v>
       </c>
       <c r="E275">
-        <v>0.01328965393112184</v>
+        <v>0.01328965393112182</v>
       </c>
       <c r="F275">
         <v>0.0009407337723424271</v>
@@ -13569,7 +13569,7 @@
         <v>59</v>
       </c>
       <c r="L275">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="M275">
         <v>198</v>
@@ -13596,7 +13596,7 @@
         <v>3</v>
       </c>
       <c r="E276">
-        <v>0.003224055950306041</v>
+        <v>0.003224055950306036</v>
       </c>
       <c r="F276">
         <v>0.0008210180623973727</v>
@@ -13617,7 +13617,7 @@
         <v>64</v>
       </c>
       <c r="L276">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="M276">
         <v>238</v>
@@ -13644,7 +13644,7 @@
         <v>8</v>
       </c>
       <c r="E277">
-        <v>0.02753037081698745</v>
+        <v>0.0275303708169874</v>
       </c>
       <c r="F277">
         <v>0.0009174311926605505</v>
@@ -13665,7 +13665,7 @@
         <v>59</v>
       </c>
       <c r="L277">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M277">
         <v>210</v>
@@ -13692,7 +13692,7 @@
         <v>26</v>
       </c>
       <c r="E278">
-        <v>0.1669525411097558</v>
+        <v>0.1669525411097556</v>
       </c>
       <c r="F278">
         <v>0.001175088131609871</v>
@@ -13740,7 +13740,7 @@
         <v>10</v>
       </c>
       <c r="E279">
-        <v>0.04096367988425561</v>
+        <v>0.0409636798842556</v>
       </c>
       <c r="F279">
         <v>0.001033057851239669</v>
@@ -13761,7 +13761,7 @@
         <v>57</v>
       </c>
       <c r="L279">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="M279">
         <v>138</v>
@@ -13836,7 +13836,7 @@
         <v>21</v>
       </c>
       <c r="E281">
-        <v>0.07388887269588612</v>
+        <v>0.07388887269588604</v>
       </c>
       <c r="F281">
         <v>0.001088139281828074</v>
@@ -13857,7 +13857,7 @@
         <v>46</v>
       </c>
       <c r="L281">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M281">
         <v>104</v>
@@ -13884,7 +13884,7 @@
         <v>17</v>
       </c>
       <c r="E282">
-        <v>0.08378694601029685</v>
+        <v>0.08378694601029672</v>
       </c>
       <c r="F282">
         <v>0.001072961373390558</v>
@@ -13905,7 +13905,7 @@
         <v>50</v>
       </c>
       <c r="L282">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M282">
         <v>113</v>
@@ -13953,7 +13953,7 @@
         <v>58</v>
       </c>
       <c r="L283">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M283">
         <v>140</v>
@@ -13980,7 +13980,7 @@
         <v>6</v>
       </c>
       <c r="E284">
-        <v>0.04032206727800922</v>
+        <v>0.04032206727800918</v>
       </c>
       <c r="F284">
         <v>0.001020408163265306</v>
@@ -14001,7 +14001,7 @@
         <v>61</v>
       </c>
       <c r="L284">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="M284">
         <v>148</v>
@@ -14028,7 +14028,7 @@
         <v>41</v>
       </c>
       <c r="E285">
-        <v>0.6366032319152638</v>
+        <v>0.6366032319152642</v>
       </c>
       <c r="F285">
         <v>0.001194743130227001</v>
@@ -14076,7 +14076,7 @@
         <v>12</v>
       </c>
       <c r="E286">
-        <v>0.03451044691911703</v>
+        <v>0.034510446919117</v>
       </c>
       <c r="F286">
         <v>0.0009615384615384616</v>
@@ -14097,7 +14097,7 @@
         <v>55</v>
       </c>
       <c r="L286">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M286">
         <v>186</v>
@@ -14124,7 +14124,7 @@
         <v>61</v>
       </c>
       <c r="E287">
-        <v>0.4390374794152565</v>
+        <v>0.4390374794152567</v>
       </c>
       <c r="F287">
         <v>0.001314060446780552</v>
@@ -14172,7 +14172,7 @@
         <v>14</v>
       </c>
       <c r="E288">
-        <v>0.04149684021094007</v>
+        <v>0.04149684021094006</v>
       </c>
       <c r="F288">
         <v>0.001049317943336831</v>
@@ -14193,7 +14193,7 @@
         <v>53</v>
       </c>
       <c r="L288">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="M288">
         <v>128</v>
@@ -14220,7 +14220,7 @@
         <v>34</v>
       </c>
       <c r="E289">
-        <v>0.6172019419608853</v>
+        <v>0.6172019419608858</v>
       </c>
       <c r="F289">
         <v>0.00116144018583043</v>
@@ -14268,7 +14268,7 @@
         <v>25</v>
       </c>
       <c r="E290">
-        <v>0.1619738294293115</v>
+        <v>0.1619738294293114</v>
       </c>
       <c r="F290">
         <v>0.001160092807424594</v>
@@ -14316,7 +14316,7 @@
         <v>6</v>
       </c>
       <c r="E291">
-        <v>0.05781159759188145</v>
+        <v>0.05781159759188143</v>
       </c>
       <c r="F291">
         <v>0.0009900990099009901</v>
@@ -14364,7 +14364,7 @@
         <v>6</v>
       </c>
       <c r="E292">
-        <v>0.05240498627857677</v>
+        <v>0.0524049862785767</v>
       </c>
       <c r="F292">
         <v>0.001044932079414838</v>
@@ -14412,7 +14412,7 @@
         <v>3</v>
       </c>
       <c r="E293">
-        <v>0.001462778058826563</v>
+        <v>0.00146277805882656</v>
       </c>
       <c r="F293">
         <v>0.0007457121551081282</v>
@@ -14433,7 +14433,7 @@
         <v>64</v>
       </c>
       <c r="L293">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="M293">
         <v>246</v>
@@ -14460,7 +14460,7 @@
         <v>3</v>
       </c>
       <c r="E294">
-        <v>0.001462778058826568</v>
+        <v>0.001462778058826558</v>
       </c>
       <c r="F294">
         <v>0.0007457121551081282</v>
@@ -14481,7 +14481,7 @@
         <v>64</v>
       </c>
       <c r="L294">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="M294">
         <v>246</v>
@@ -14508,7 +14508,7 @@
         <v>25</v>
       </c>
       <c r="E295">
-        <v>0.1002666576929728</v>
+        <v>0.1002666576929727</v>
       </c>
       <c r="F295">
         <v>0.001141552511415525</v>
@@ -14556,7 +14556,7 @@
         <v>26</v>
       </c>
       <c r="E296">
-        <v>0.3930655641273039</v>
+        <v>0.3930655641273042</v>
       </c>
       <c r="F296">
         <v>0.001234567901234568</v>
@@ -14604,7 +14604,7 @@
         <v>44</v>
       </c>
       <c r="E297">
-        <v>0.5705725729084505</v>
+        <v>0.5705725729084509</v>
       </c>
       <c r="F297">
         <v>0.001298701298701299</v>
@@ -14700,7 +14700,7 @@
         <v>32</v>
       </c>
       <c r="E299">
-        <v>0.2871043617036991</v>
+        <v>0.2871043617036992</v>
       </c>
       <c r="F299">
         <v>0.001226993865030675</v>
@@ -14769,7 +14769,7 @@
         <v>50</v>
       </c>
       <c r="L300">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M300">
         <v>145</v>
@@ -14796,7 +14796,7 @@
         <v>10</v>
       </c>
       <c r="E301">
-        <v>0.01832840610904557</v>
+        <v>0.01832840610904552</v>
       </c>
       <c r="F301">
         <v>0.0009560229445506692</v>
@@ -14817,7 +14817,7 @@
         <v>57</v>
       </c>
       <c r="L301">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="M301">
         <v>188</v>
@@ -14844,7 +14844,7 @@
         <v>12</v>
       </c>
       <c r="E302">
-        <v>0.1479835432805175</v>
+        <v>0.1479835432805174</v>
       </c>
       <c r="F302">
         <v>0.001063829787234043</v>
@@ -14892,7 +14892,7 @@
         <v>32</v>
       </c>
       <c r="E303">
-        <v>0.18984615476275</v>
+        <v>0.1898461547627502</v>
       </c>
       <c r="F303">
         <v>0.001221001221001221</v>
@@ -14940,7 +14940,7 @@
         <v>5</v>
       </c>
       <c r="E304">
-        <v>0.01910761619681391</v>
+        <v>0.01910761619681388</v>
       </c>
       <c r="F304">
         <v>0.0009737098344693282</v>
@@ -14961,7 +14961,7 @@
         <v>62</v>
       </c>
       <c r="L304">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="M304">
         <v>178</v>
@@ -14988,7 +14988,7 @@
         <v>4</v>
       </c>
       <c r="E305">
-        <v>0.003703974744133536</v>
+        <v>0.00370397474413353</v>
       </c>
       <c r="F305">
         <v>0.0007867820613690008</v>
@@ -15009,7 +15009,7 @@
         <v>63</v>
       </c>
       <c r="L305">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="M305">
         <v>244</v>
@@ -15036,7 +15036,7 @@
         <v>3</v>
       </c>
       <c r="E306">
-        <v>0.008110103308476365</v>
+        <v>0.008110103308476344</v>
       </c>
       <c r="F306">
         <v>0.0009000900090009001</v>
@@ -15057,7 +15057,7 @@
         <v>64</v>
       </c>
       <c r="L306">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="M306">
         <v>218</v>
@@ -15153,7 +15153,7 @@
         <v>64</v>
       </c>
       <c r="L308">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M308">
         <v>209</v>
@@ -15180,7 +15180,7 @@
         <v>22</v>
       </c>
       <c r="E309">
-        <v>0.09586555052519173</v>
+        <v>0.09586555052519176</v>
       </c>
       <c r="F309">
         <v>0.001104972375690608</v>
@@ -15201,7 +15201,7 @@
         <v>45</v>
       </c>
       <c r="L309">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M309">
         <v>93</v>
@@ -15276,7 +15276,7 @@
         <v>10</v>
       </c>
       <c r="E311">
-        <v>0.05009233266020927</v>
+        <v>0.05009233266020925</v>
       </c>
       <c r="F311">
         <v>0.0009970089730807576</v>
@@ -15324,7 +15324,7 @@
         <v>11</v>
       </c>
       <c r="E312">
-        <v>0.02992340845065002</v>
+        <v>0.02992340845064995</v>
       </c>
       <c r="F312">
         <v>0.001001001001001001</v>
@@ -15345,7 +15345,7 @@
         <v>56</v>
       </c>
       <c r="L312">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M312">
         <v>161</v>
@@ -15372,7 +15372,7 @@
         <v>7</v>
       </c>
       <c r="E313">
-        <v>0.03125744335822791</v>
+        <v>0.03125744335822794</v>
       </c>
       <c r="F313">
         <v>0.0009532888465204957</v>
@@ -15393,7 +15393,7 @@
         <v>60</v>
       </c>
       <c r="L313">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="M313">
         <v>190</v>
@@ -15468,7 +15468,7 @@
         <v>8</v>
       </c>
       <c r="E315">
-        <v>0.01198749025781997</v>
+        <v>0.01198749025781996</v>
       </c>
       <c r="F315">
         <v>0.0009082652134423251</v>
@@ -15489,7 +15489,7 @@
         <v>59</v>
       </c>
       <c r="L315">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="M315">
         <v>214</v>
@@ -15516,7 +15516,7 @@
         <v>8</v>
       </c>
       <c r="E316">
-        <v>0.05570077917551073</v>
+        <v>0.05570077917551079</v>
       </c>
       <c r="F316">
         <v>0.0009900990099009901</v>
@@ -15612,7 +15612,7 @@
         <v>12</v>
       </c>
       <c r="E318">
-        <v>0.04549053863550449</v>
+        <v>0.04549053863550445</v>
       </c>
       <c r="F318">
         <v>0.0009940357852882703</v>
@@ -15633,7 +15633,7 @@
         <v>55</v>
       </c>
       <c r="L318">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="M318">
         <v>167</v>
@@ -15660,7 +15660,7 @@
         <v>20</v>
       </c>
       <c r="E319">
-        <v>0.1043944598069685</v>
+        <v>0.1043944598069684</v>
       </c>
       <c r="F319">
         <v>0.001107419712070875</v>
@@ -15708,7 +15708,7 @@
         <v>7</v>
       </c>
       <c r="E320">
-        <v>0.01531606184160937</v>
+        <v>0.01531606184160935</v>
       </c>
       <c r="F320">
         <v>0.0009057971014492754</v>
@@ -15729,7 +15729,7 @@
         <v>60</v>
       </c>
       <c r="L320">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="M320">
         <v>215</v>
@@ -15756,7 +15756,7 @@
         <v>21</v>
       </c>
       <c r="E321">
-        <v>0.1893674266679495</v>
+        <v>0.1893674266679497</v>
       </c>
       <c r="F321">
         <v>0.001054852320675105</v>
@@ -15804,7 +15804,7 @@
         <v>40</v>
       </c>
       <c r="E322">
-        <v>0.6771638472564097</v>
+        <v>0.6771638472564101</v>
       </c>
       <c r="F322">
         <v>0.001230012300123001</v>
@@ -15852,7 +15852,7 @@
         <v>6</v>
       </c>
       <c r="E323">
-        <v>0.007653380926048059</v>
+        <v>0.007653380926048068</v>
       </c>
       <c r="F323">
         <v>0.0008032128514056225</v>
@@ -15873,7 +15873,7 @@
         <v>61</v>
       </c>
       <c r="L323">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="M323">
         <v>242</v>
@@ -15900,7 +15900,7 @@
         <v>11</v>
       </c>
       <c r="E324">
-        <v>0.01744735345694175</v>
+        <v>0.01744735345694174</v>
       </c>
       <c r="F324">
         <v>0.0009025270758122744</v>
@@ -15921,7 +15921,7 @@
         <v>56</v>
       </c>
       <c r="L324">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="M324">
         <v>217</v>
@@ -15948,7 +15948,7 @@
         <v>27</v>
       </c>
       <c r="E325">
-        <v>0.04750626512995091</v>
+        <v>0.047506265129951</v>
       </c>
       <c r="F325">
         <v>0.001017293997965412</v>
@@ -15969,7 +15969,7 @@
         <v>40</v>
       </c>
       <c r="L325">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M325">
         <v>150</v>
@@ -15996,7 +15996,7 @@
         <v>10</v>
       </c>
       <c r="E326">
-        <v>0.01658342105041324</v>
+        <v>0.01658342105041323</v>
       </c>
       <c r="F326">
         <v>0.0009000900090009001</v>
@@ -16017,7 +16017,7 @@
         <v>57</v>
       </c>
       <c r="L326">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="M326">
         <v>218</v>
@@ -16044,7 +16044,7 @@
         <v>13</v>
       </c>
       <c r="E327">
-        <v>0.06361632245626866</v>
+        <v>0.06361632245626873</v>
       </c>
       <c r="F327">
         <v>0.001004016064257028</v>
@@ -16065,7 +16065,7 @@
         <v>54</v>
       </c>
       <c r="L327">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M327">
         <v>159</v>
@@ -16092,7 +16092,7 @@
         <v>33</v>
       </c>
       <c r="E328">
-        <v>0.6100705664560868</v>
+        <v>0.6100705664560874</v>
       </c>
       <c r="F328">
         <v>0.00112739571589628</v>
@@ -16140,7 +16140,7 @@
         <v>7</v>
       </c>
       <c r="E329">
-        <v>0.06579423653942765</v>
+        <v>0.06579423653942758</v>
       </c>
       <c r="F329">
         <v>0.001036269430051813</v>
@@ -16161,7 +16161,7 @@
         <v>60</v>
       </c>
       <c r="L329">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M329">
         <v>136</v>
@@ -16188,7 +16188,7 @@
         <v>18</v>
       </c>
       <c r="E330">
-        <v>0.2368366138336075</v>
+        <v>0.2368366138336077</v>
       </c>
       <c r="F330">
         <v>0.001017293997965412</v>
@@ -16284,7 +16284,7 @@
         <v>61</v>
       </c>
       <c r="E332">
-        <v>0.8294001560615306</v>
+        <v>0.8294001560615312</v>
       </c>
       <c r="F332">
         <v>0.001319261213720317</v>
@@ -16332,7 +16332,7 @@
         <v>12</v>
       </c>
       <c r="E333">
-        <v>0.09784156588767265</v>
+        <v>0.09784156588767259</v>
       </c>
       <c r="F333">
         <v>0.001078748651564185</v>
@@ -16353,7 +16353,7 @@
         <v>55</v>
       </c>
       <c r="L333">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M333">
         <v>110</v>
@@ -16380,7 +16380,7 @@
         <v>48</v>
       </c>
       <c r="E334">
-        <v>0.7410838215286381</v>
+        <v>0.7410838215286385</v>
       </c>
       <c r="F334">
         <v>0.001257861635220126</v>
@@ -16476,7 +16476,7 @@
         <v>11</v>
       </c>
       <c r="E336">
-        <v>0.09830608544164827</v>
+        <v>0.09830608544164825</v>
       </c>
       <c r="F336">
         <v>0.001044932079414838</v>
@@ -16497,7 +16497,7 @@
         <v>56</v>
       </c>
       <c r="L336">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M336">
         <v>131</v>
@@ -16524,7 +16524,7 @@
         <v>39</v>
       </c>
       <c r="E337">
-        <v>0.214752077039961</v>
+        <v>0.2147520770399609</v>
       </c>
       <c r="F337">
         <v>0.001242236024844721</v>
@@ -16572,7 +16572,7 @@
         <v>10</v>
       </c>
       <c r="E338">
-        <v>0.04633988099417916</v>
+        <v>0.04633988099417913</v>
       </c>
       <c r="F338">
         <v>0.000998003992015968</v>
@@ -16593,7 +16593,7 @@
         <v>57</v>
       </c>
       <c r="L338">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M338">
         <v>164</v>
@@ -16668,7 +16668,7 @@
         <v>19</v>
       </c>
       <c r="E340">
-        <v>0.1070522705404515</v>
+        <v>0.1070522705404514</v>
       </c>
       <c r="F340">
         <v>0.001153402537485583</v>
@@ -16716,7 +16716,7 @@
         <v>5</v>
       </c>
       <c r="E341">
-        <v>0.00790709802901554</v>
+        <v>0.007907098029015536</v>
       </c>
       <c r="F341">
         <v>0.0008665511265164644</v>
@@ -16737,7 +16737,7 @@
         <v>62</v>
       </c>
       <c r="L341">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="M341">
         <v>228</v>
@@ -16812,7 +16812,7 @@
         <v>12</v>
       </c>
       <c r="E343">
-        <v>0.05317189243798529</v>
+        <v>0.05317189243798531</v>
       </c>
       <c r="F343">
         <v>0.0009505703422053232</v>
@@ -16860,7 +16860,7 @@
         <v>24</v>
       </c>
       <c r="E344">
-        <v>0.1338600588194085</v>
+        <v>0.1338600588194086</v>
       </c>
       <c r="F344">
         <v>0.001118568232662192</v>
@@ -16908,7 +16908,7 @@
         <v>16</v>
       </c>
       <c r="E345">
-        <v>0.2090500563935286</v>
+        <v>0.2090500563935289</v>
       </c>
       <c r="F345">
         <v>0.001016260162601626</v>
@@ -16956,7 +16956,7 @@
         <v>13</v>
       </c>
       <c r="E346">
-        <v>0.06772223124059859</v>
+        <v>0.06772223124059862</v>
       </c>
       <c r="F346">
         <v>0.001041666666666667</v>
@@ -16977,7 +16977,7 @@
         <v>54</v>
       </c>
       <c r="L346">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M346">
         <v>133</v>
@@ -17025,7 +17025,7 @@
         <v>63</v>
       </c>
       <c r="L347">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="M347">
         <v>213</v>
@@ -17121,7 +17121,7 @@
         <v>62</v>
       </c>
       <c r="L349">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="M349">
         <v>211</v>
@@ -17148,7 +17148,7 @@
         <v>12</v>
       </c>
       <c r="E350">
-        <v>0.03727009522580049</v>
+        <v>0.03727009522580046</v>
       </c>
       <c r="F350">
         <v>0.001022494887525562</v>
@@ -17169,7 +17169,7 @@
         <v>55</v>
       </c>
       <c r="L350">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="M350">
         <v>146</v>
@@ -17196,7 +17196,7 @@
         <v>11</v>
       </c>
       <c r="E351">
-        <v>0.03897327675682485</v>
+        <v>0.03897327675682481</v>
       </c>
       <c r="F351">
         <v>0.00101010101010101</v>
@@ -17217,7 +17217,7 @@
         <v>56</v>
       </c>
       <c r="L351">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M351">
         <v>155</v>
@@ -17265,7 +17265,7 @@
         <v>64</v>
       </c>
       <c r="L352">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="M352">
         <v>245</v>
@@ -17292,7 +17292,7 @@
         <v>19</v>
       </c>
       <c r="E353">
-        <v>0.07090953292899752</v>
+        <v>0.07090953292899753</v>
       </c>
       <c r="F353">
         <v>0.001082251082251082</v>
@@ -17313,7 +17313,7 @@
         <v>48</v>
       </c>
       <c r="L353">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M353">
         <v>108</v>
@@ -17388,7 +17388,7 @@
         <v>25</v>
       </c>
       <c r="E355">
-        <v>0.1163565292449268</v>
+        <v>0.1163565292449267</v>
       </c>
       <c r="F355">
         <v>0.001204819277108434</v>
@@ -17436,7 +17436,7 @@
         <v>28</v>
       </c>
       <c r="E356">
-        <v>0.1044766255075167</v>
+        <v>0.1044766255075166</v>
       </c>
       <c r="F356">
         <v>0.001132502831257078</v>
@@ -17484,7 +17484,7 @@
         <v>61</v>
       </c>
       <c r="E357">
-        <v>0.3928701474974503</v>
+        <v>0.3928701474974506</v>
       </c>
       <c r="F357">
         <v>0.001322751322751323</v>
@@ -17532,7 +17532,7 @@
         <v>11</v>
       </c>
       <c r="E358">
-        <v>0.04746125266842012</v>
+        <v>0.04746125266842018</v>
       </c>
       <c r="F358">
         <v>0.001008064516129032</v>
@@ -17553,7 +17553,7 @@
         <v>56</v>
       </c>
       <c r="L358">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="M358">
         <v>156</v>
@@ -17580,7 +17580,7 @@
         <v>29</v>
       </c>
       <c r="E359">
-        <v>0.1112235821798969</v>
+        <v>0.1112235821798968</v>
       </c>
       <c r="F359">
         <v>0.001166861143523921</v>
@@ -17628,7 +17628,7 @@
         <v>33</v>
       </c>
       <c r="E360">
-        <v>0.2371233612026562</v>
+        <v>0.2371233612026564</v>
       </c>
       <c r="F360">
         <v>0.001204819277108434</v>
@@ -17676,7 +17676,7 @@
         <v>30</v>
       </c>
       <c r="E361">
-        <v>0.2538242622382387</v>
+        <v>0.2538242622382386</v>
       </c>
       <c r="F361">
         <v>0.001203369434416366</v>
@@ -17820,7 +17820,7 @@
         <v>6</v>
       </c>
       <c r="E364">
-        <v>0.05652076810333861</v>
+        <v>0.05652076810333864</v>
       </c>
       <c r="F364">
         <v>0.0009624639076034649</v>
@@ -17868,7 +17868,7 @@
         <v>61</v>
       </c>
       <c r="E365">
-        <v>0.3179365272074254</v>
+        <v>0.3179365272074252</v>
       </c>
       <c r="F365">
         <v>0.001265822784810127</v>
@@ -17916,7 +17916,7 @@
         <v>5</v>
       </c>
       <c r="E366">
-        <v>0.008986312115614391</v>
+        <v>0.008986312115614389</v>
       </c>
       <c r="F366">
         <v>0.0008818342151675485</v>
@@ -17937,7 +17937,7 @@
         <v>62</v>
       </c>
       <c r="L366">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="M366">
         <v>225</v>
@@ -17964,7 +17964,7 @@
         <v>4</v>
       </c>
       <c r="E367">
-        <v>0.02868319424990204</v>
+        <v>0.02868319424990203</v>
       </c>
       <c r="F367">
         <v>0.0009514747859181732</v>
@@ -17985,7 +17985,7 @@
         <v>63</v>
       </c>
       <c r="L367">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M367">
         <v>192</v>
@@ -18012,7 +18012,7 @@
         <v>11</v>
       </c>
       <c r="E368">
-        <v>0.0990044413987234</v>
+        <v>0.09900444139872341</v>
       </c>
       <c r="F368">
         <v>0.00112739571589628</v>
@@ -18033,7 +18033,7 @@
         <v>56</v>
       </c>
       <c r="L368">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M368">
         <v>81</v>
@@ -18060,7 +18060,7 @@
         <v>104</v>
       </c>
       <c r="E369">
-        <v>0.6160822875887232</v>
+        <v>0.6160822875887229</v>
       </c>
       <c r="F369">
         <v>0.001457725947521866</v>
@@ -18108,7 +18108,7 @@
         <v>62</v>
       </c>
       <c r="E370">
-        <v>0.318401452683127</v>
+        <v>0.3184014526831269</v>
       </c>
       <c r="F370">
         <v>0.001312335958005249</v>
@@ -18156,7 +18156,7 @@
         <v>19</v>
       </c>
       <c r="E371">
-        <v>0.1434973752342217</v>
+        <v>0.1434973752342216</v>
       </c>
       <c r="F371">
         <v>0.00112739571589628</v>
@@ -18252,7 +18252,7 @@
         <v>7</v>
       </c>
       <c r="E373">
-        <v>0.02879154383480169</v>
+        <v>0.02879154383480172</v>
       </c>
       <c r="F373">
         <v>0.0009389671361502347</v>
@@ -18273,7 +18273,7 @@
         <v>60</v>
       </c>
       <c r="L373">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M373">
         <v>199</v>
@@ -18300,7 +18300,7 @@
         <v>7</v>
       </c>
       <c r="E374">
-        <v>0.06807400208897194</v>
+        <v>0.068074002088972</v>
       </c>
       <c r="F374">
         <v>0.0009523809523809524</v>
@@ -18321,7 +18321,7 @@
         <v>60</v>
       </c>
       <c r="L374">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M374">
         <v>191</v>
@@ -18348,7 +18348,7 @@
         <v>7</v>
       </c>
       <c r="E375">
-        <v>0.0529111984216075</v>
+        <v>0.05291119842160743</v>
       </c>
       <c r="F375">
         <v>0.001054852320675105</v>
@@ -18396,7 +18396,7 @@
         <v>9</v>
       </c>
       <c r="E376">
-        <v>0.04461794224447049</v>
+        <v>0.04461794224447044</v>
       </c>
       <c r="F376">
         <v>0.001012145748987854</v>
@@ -18417,7 +18417,7 @@
         <v>58</v>
       </c>
       <c r="L376">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M376">
         <v>154</v>
@@ -18444,7 +18444,7 @@
         <v>17</v>
       </c>
       <c r="E377">
-        <v>0.07692384392885079</v>
+        <v>0.07692384392885074</v>
       </c>
       <c r="F377">
         <v>0.001061571125265393</v>
@@ -18465,7 +18465,7 @@
         <v>50</v>
       </c>
       <c r="L377">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M377">
         <v>119</v>
@@ -18492,7 +18492,7 @@
         <v>46</v>
       </c>
       <c r="E378">
-        <v>0.1740113387496378</v>
+        <v>0.1740113387496375</v>
       </c>
       <c r="F378">
         <v>0.001176470588235294</v>
@@ -18540,7 +18540,7 @@
         <v>29</v>
       </c>
       <c r="E379">
-        <v>0.1875336614756883</v>
+        <v>0.1875336614756882</v>
       </c>
       <c r="F379">
         <v>0.001190476190476191</v>
@@ -18636,7 +18636,7 @@
         <v>10</v>
       </c>
       <c r="E381">
-        <v>0.05925770334816909</v>
+        <v>0.05925770334816911</v>
       </c>
       <c r="F381">
         <v>0.0009775171065493646</v>
@@ -18684,7 +18684,7 @@
         <v>13</v>
       </c>
       <c r="E382">
-        <v>0.04930888615707067</v>
+        <v>0.04930888615707063</v>
       </c>
       <c r="F382">
         <v>0.001050420168067227</v>
@@ -18705,7 +18705,7 @@
         <v>54</v>
       </c>
       <c r="L382">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="M382">
         <v>127</v>
@@ -18732,7 +18732,7 @@
         <v>13</v>
       </c>
       <c r="E383">
-        <v>0.04930888615707069</v>
+        <v>0.04930888615707063</v>
       </c>
       <c r="F383">
         <v>0.001050420168067227</v>
